--- a/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
+++ b/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\experiments\HI_calculations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\experiments\HI_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5223D14D-DAA0-4611-B567-A270C0DF2E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD542628-C827-4A20-B791-D2F577DF49C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -271,7 +271,7 @@
     <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -280,7 +280,7 @@
     <xf numFmtId="22" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -289,7 +289,7 @@
     <xf numFmtId="22" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -298,7 +298,7 @@
     <xf numFmtId="22" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -307,7 +307,7 @@
     <xf numFmtId="22" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -325,22 +325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -352,10 +337,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3511,6 +3493,835 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.14977602799650044"/>
+                  <c:y val="-4.724883347914844E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.453436795025429</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14144997157405101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13607881876945299</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61769731984154397</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66455526442613699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>167.04416760000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>162.5418607</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>174.6761387</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>287.8289474</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>243.34662650000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-25CE-4B85-94F2-97BE322DD0C0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="919728464"/>
+        <c:axId val="420663184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="919728464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="420663184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="420663184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="919728464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Max Depth</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - Peak SSC</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.689204790622849E-2"/>
+                  <c:y val="-3.7657682708157364E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.453436795025429</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14144997157405101</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13607881876945299</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61769731984154397</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66455526442613699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$14:$E$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.262211557214444</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15997395020695501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.5566841037180299E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.62020718230999505</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.78199948801270402</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B298-4ADC-A1B3-4B9CC8A35550}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1720633552"/>
+        <c:axId val="1720623952"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1720633552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SSC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> concentration (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1720623952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1720623952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1720633552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -4381,7 +5192,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5151,7 +5962,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5921,7 +6732,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6482,7 +7293,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7021,7 +7832,469 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Max Depth</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - Peak POC</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.18188667782560905"/>
+                  <c:y val="-0.13955211302208961"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$14:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12.33049707</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.04121088</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.93014432</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.660150940000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.72610796</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>22.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.992000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.641999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.291</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.274999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-205E-4FB3-93AC-B66AAE226AC6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1720633552"/>
+        <c:axId val="1720623952"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1720633552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>POC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> concentration (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1720623952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1720623952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1720633552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7560,7 +8833,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8133,469 +9406,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Max Depth</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> - Peak POC</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.18188667782560905"/>
-                  <c:y val="-0.13955211302208961"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$F$14:$F$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>12.33049707</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>12.04121088</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10.93014432</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>24.660150940000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.72610796</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-205E-4FB3-93AC-B66AAE226AC6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1720633552"/>
-        <c:axId val="1720623952"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1720633552"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>POC</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> concentration (mg/L)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1720623952"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1720623952"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1720633552"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9146,7 +9957,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9697,7 +10508,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -10252,7 +11063,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -10788,7 +11599,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -11324,7 +12135,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -11873,7 +12684,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -12409,7 +13220,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -12705,1097 +13516,6 @@
                 <a:r>
                   <a:rPr lang="en-US"/>
                   <a:t>DOC (mg/L)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1366990752"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1366990752"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>POC</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> (mg/L)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1366993632"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="108"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="8"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>SSC (mg/L)</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> vs SSC (uL/L) - Exp 5</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.31649197338704754"/>
-                  <c:y val="2.6708223972003498E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'constituent correlations'!$E$59:$E$71</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>90.43</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>426.28</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>258.72000000000003</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>227.15</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>176.59</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>181.06</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>157</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>134.22999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.31</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>88.72</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>71.86</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>59.21</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>51.52</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'constituent correlations'!$F$59:$F$71</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>62.139769450000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>243.34662650000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>134.52914799999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>135.40290619999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>99.901736</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>98.606470540000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>93.938898870000003</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>56.216392370000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>56.813503500000003</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>48.527718370000002</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>41.608876559999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>27.029240720000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>22.11845662</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BC67-4846-9CB5-81638E7F65CF}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1366993632"/>
-        <c:axId val="1366990752"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1366993632"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>LISST (uL/L)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1366990752"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1366990752"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>SSC (mg/L)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1366993632"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="108"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="8"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>SSC (mg/L)</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> vs POC (mg/L) - Exp 5</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.22211061455155942"/>
-                  <c:y val="4.6640191715166042E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'constituent correlations'!$F$59:$F$71</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>62.139769450000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>243.34662650000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>134.52914799999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>135.40290619999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>99.901736</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>98.606470540000004</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>93.938898870000003</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>56.216392370000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>56.813503500000003</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>48.527718370000002</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>41.608876559999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>27.029240720000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>22.11845662</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'constituent correlations'!$H$59:$H$71</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>5.3161272320000004</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.72610796</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11.66797622</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.6757924820000003</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.6309098449999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-79FA-4733-87C8-A1E4225327B4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1366993632"/>
-        <c:axId val="1366990752"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1366993632"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>SSC (mg/L)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -14541,6 +14261,1097 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>SSC (mg/L)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> vs SSC (uL/L) - Exp 5</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.31649197338704754"/>
+                  <c:y val="2.6708223972003498E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'constituent correlations'!$E$59:$E$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>90.43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>426.28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>258.72000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>227.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>176.59</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>181.06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>134.22999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.31</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>88.72</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>71.86</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>59.21</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>51.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'constituent correlations'!$F$59:$F$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>62.139769450000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>243.34662650000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>134.52914799999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>135.40290619999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>99.901736</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>98.606470540000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>93.938898870000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>56.216392370000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>56.813503500000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48.527718370000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>41.608876559999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.029240720000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22.11845662</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BC67-4846-9CB5-81638E7F65CF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1366993632"/>
+        <c:axId val="1366990752"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1366993632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>LISST (uL/L)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366990752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1366990752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SSC (mg/L)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366993632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SSC (mg/L)</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> vs POC (mg/L) - Exp 5</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.22211061455155942"/>
+                  <c:y val="4.6640191715166042E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'constituent correlations'!$F$59:$F$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>62.139769450000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>243.34662650000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>134.52914799999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>135.40290619999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>99.901736</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>98.606470540000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>93.938898870000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>56.216392370000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>56.813503500000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48.527718370000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>41.608876559999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.029240720000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>22.11845662</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'constituent correlations'!$H$59:$H$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>5.3161272320000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.72610796</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.66797622</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.6757924820000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.6309098449999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-79FA-4733-87C8-A1E4225327B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1366993632"/>
+        <c:axId val="1366990752"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1366993632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>SSC (mg/L)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366990752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1366990752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>POC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366993632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>DOC (mg/L)</a:t>
             </a:r>
             <a:r>
@@ -15050,7 +15861,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -15601,7 +16412,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -16131,7 +16942,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -16669,7 +17480,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart36.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -17214,7 +18025,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart37.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -17744,7 +18555,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart38.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -23836,14 +24647,82 @@
 </file>
 
 <file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -23854,8 +24733,8 @@
 </file>
 
 <file path=xl/charts/colors19.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
 </cs:colorStyle>
 </file>
 
@@ -23900,8 +24779,8 @@
 </file>
 
 <file path=xl/charts/colors20.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
 </cs:colorStyle>
 </file>
 
@@ -23912,14 +24791,14 @@
 </file>
 
 <file path=xl/charts/colors22.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
-  <a:schemeClr val="accent4"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+  <a:schemeClr val="accent3"/>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors23.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
-  <a:schemeClr val="accent4"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="16">
+  <a:schemeClr val="accent3"/>
 </cs:colorStyle>
 </file>
 
@@ -23930,14 +24809,14 @@
 </file>
 
 <file path=xl/charts/colors25.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
-  <a:schemeClr val="accent5"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
+  <a:schemeClr val="accent4"/>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors26.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
-  <a:schemeClr val="accent5"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="17">
+  <a:schemeClr val="accent4"/>
 </cs:colorStyle>
 </file>
 
@@ -23948,14 +24827,14 @@
 </file>
 
 <file path=xl/charts/colors28.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
-  <a:schemeClr val="accent6"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
+  <a:schemeClr val="accent5"/>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors29.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
-  <a:schemeClr val="accent6"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
+  <a:schemeClr val="accent5"/>
 </cs:colorStyle>
 </file>
 
@@ -24006,14 +24885,14 @@
 </file>
 
 <file path=xl/charts/colors31.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
+  <a:schemeClr val="accent6"/>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors32.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
+  <a:schemeClr val="accent6"/>
 </cs:colorStyle>
 </file>
 
@@ -24036,6 +24915,18 @@
 </file>
 
 <file path=xl/charts/colors36.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors37.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors38.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
@@ -39246,6 +40137,1038 @@
 </file>
 
 <file path=xl/charts/style36.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style37.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style38.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -43308,6 +45231,80 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C49F0A67-6375-22F4-1E97-0A1B870E9C25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1409699</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9322E80E-5E18-4245-956A-A833C35FD171}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -44523,22 +46520,22 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="1"/>
@@ -44554,28 +46551,28 @@
       <c r="L4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="5">
         <v>2.1877294251263</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="5">
         <f>LOG10(B5)</f>
         <v>0.33999360813627283</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="5">
         <v>0.71803227014055304</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="5">
         <v>0.453436795025429</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="8">
         <f>MAX('constituent correlations'!F4:F17)</f>
         <v>167.04416760000001</v>
       </c>
@@ -44601,23 +46598,23 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="5">
         <v>1.32397503582887</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="5">
         <f t="shared" ref="C6:C11" si="0">LOG10(B6)</f>
         <v>0.12187979635445149</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="5">
         <v>0.24125163857843901</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="5">
         <v>0.14144997157405101</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="8">
         <f>MAX('constituent correlations'!F18:F33)</f>
         <v>162.5418607</v>
       </c>
@@ -44643,23 +46640,23 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="5">
         <v>1.3077318896824699</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="5">
         <f t="shared" si="0"/>
         <v>0.11651871435007208</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="5">
         <v>0.39340714771465102</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="5">
         <v>0.13607881876945299</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="8">
         <f>MAX('constituent correlations'!F34:F46)</f>
         <v>174.6761387</v>
       </c>
@@ -44685,23 +46682,23 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="5">
         <v>2.1693958595572602</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="5">
         <f t="shared" si="0"/>
         <v>0.33633880694037765</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="5">
         <v>0.79163162608253801</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="5">
         <v>0.61769731984154397</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="8">
         <f>MAX('constituent correlations'!F47:F58)</f>
         <v>287.8289474</v>
       </c>
@@ -44727,23 +46724,23 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="31">
         <v>1.57422422167948</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="31">
         <f t="shared" si="0"/>
         <v>0.19706659035014132</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="31">
         <v>0.44150780994259298</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="31">
         <v>0.66455526442613699</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="32">
         <f>MAX('constituent correlations'!F59:F71)</f>
         <v>243.34662650000001</v>
       </c>
@@ -44831,7 +46828,10 @@
         <f>MAX('constituent correlations'!F83:F92)</f>
         <v>240.01979539999999</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <f>F10/F11</f>
+        <v>0.18702886578662589</v>
+      </c>
       <c r="H11" s="1" t="s">
         <v>9</v>
       </c>
@@ -44859,136 +46859,136 @@
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="5">
         <v>1.49932904478425</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="5">
         <f>LOG10(B14)</f>
         <v>0.17589695416394432</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="5">
         <v>0.77642606785996804</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="5">
         <v>0.262211557214444</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="8">
         <f>MAX('constituent correlations'!H4:H17)</f>
         <v>12.33049707</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="5">
         <v>1.1773740554885099</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="5">
         <f t="shared" ref="C15:C20" si="1">LOG10(B15)</f>
         <v>7.0914461506453946E-2</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="5">
         <v>0.18229454485882499</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="5">
         <v>0.15997395020695501</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="8">
         <f>MAX('constituent correlations'!H18:H33)</f>
         <v>12.04121088</v>
       </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="5">
         <v>1.0062499424026501</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="5">
         <f t="shared" si="1"/>
         <v>2.7058685170807499E-3</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="6">
         <v>-0.240947268722355</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="6">
         <v>-2.5566841037180299E-3</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="8">
         <f>MAX('constituent correlations'!H34:H46)</f>
         <v>10.93014432</v>
       </c>
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="5">
         <v>1.88871548942613</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="5">
         <f t="shared" si="1"/>
         <v>0.27616654199898055</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="5">
         <v>0.88806250457032299</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="5">
         <v>0.62020718230999505</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="8">
         <f>MAX('constituent correlations'!H47:H58)</f>
         <v>24.660150940000001</v>
       </c>
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="31">
         <v>1.8348553138688299</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="31">
         <f t="shared" si="1"/>
         <v>0.26360182397461063</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="31">
         <v>0.92716260893139602</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="31">
         <v>0.78199948801270402</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="32">
         <f>MAX('constituent correlations'!H59:H71)</f>
         <v>20.72610796</v>
       </c>
@@ -45038,7 +47038,10 @@
         <f>MAX('constituent correlations'!H83:H92)</f>
         <v>17.196570690000001</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1">
+        <f>F19/F20</f>
+        <v>0.28681436519597148</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
@@ -45046,136 +47049,136 @@
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="5">
         <v>1.05312198074008</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="5">
         <f>LOG10(B23)</f>
         <v>2.2478677447762781E-2</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="33">
         <v>0.29004509914582</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="5">
         <v>8.2872285708523799E-2</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="1">
         <f>MAX('constituent correlations'!G4:G17)</f>
         <v>2.64</v>
       </c>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="6">
         <v>0.96447744969623705</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="6">
         <f t="shared" ref="C24:C29" si="2">LOG10(B24)</f>
         <v>-1.5707922076061909E-2</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="7">
         <v>-0.88020825662958402</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="6">
         <v>-0.120864394889326</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="1">
         <f>MAX('constituent correlations'!G18:G33)</f>
         <v>3.0089999999999999</v>
       </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="5">
         <v>1.0170677163786801</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="5">
         <f t="shared" si="2"/>
         <v>7.3498692163067999E-3</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="33">
         <v>0.47015675471698098</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="5">
         <v>1.1974710137234199E-2</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="1">
         <f>MAX('constituent correlations'!G34:G46)</f>
         <v>2.8980000000000001</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="6">
         <v>0.96859119932537396</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="6">
         <f t="shared" si="2"/>
         <v>-1.3859481295871032E-2</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="7">
         <v>-0.50732452729004396</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="6">
         <v>-9.3327819128066702E-2</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="1">
         <f>MAX('constituent correlations'!G47:G58)</f>
         <v>2.3029999999999999</v>
       </c>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="34">
         <v>0.966529928734157</v>
       </c>
-      <c r="C27" s="40">
+      <c r="C27" s="34">
         <f t="shared" si="2"/>
         <v>-1.4784693437961027E-2</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="35">
         <v>-0.92976462887333999</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="34">
         <v>-7.3285474508812898E-2</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="30">
         <f>MAX('constituent correlations'!G59:G71)</f>
         <v>2.883</v>
       </c>
@@ -45225,7 +47228,10 @@
         <f>MAX('constituent correlations'!G83:G92)</f>
         <v>3.1349999999999998</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1">
+        <f>F28/F29</f>
+        <v>1.1614035087719299</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B30" s="1"/>

--- a/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
+++ b/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\experiments\HI_calculations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\experiments\HI_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD542628-C827-4A20-B791-D2F577DF49C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B6D383-5643-4A62-8144-24F1BEF0648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="36">
   <si>
     <t>DOC (mg/L)</t>
   </si>
@@ -133,6 +133,18 @@
   </si>
   <si>
     <t>% bed moved</t>
+  </si>
+  <si>
+    <t>Experiment 8</t>
+  </si>
+  <si>
+    <t>PP (mg/L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP (mg/L) </t>
+  </si>
+  <si>
+    <t>SRP (mg/L)</t>
   </si>
 </sst>
 </file>
@@ -45317,13 +45329,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
@@ -45353,13 +45365,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>409575</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -45391,13 +45403,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -45429,14 +45441,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>495301</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
@@ -45467,13 +45479,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
@@ -45505,13 +45517,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>314325</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -45543,13 +45555,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
@@ -45581,13 +45593,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -45619,13 +45631,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>276225</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -45657,13 +45669,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>90487</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
@@ -45695,13 +45707,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -45733,13 +45745,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>276225</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
@@ -45771,13 +45783,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>61912</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
@@ -45809,13 +45821,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
@@ -45847,13 +45859,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -45885,13 +45897,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>447675</xdr:colOff>
       <xdr:row>64</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
@@ -45923,13 +45935,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
       <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -45961,13 +45973,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
@@ -45999,13 +46011,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>502920</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>573405</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -46037,13 +46049,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>5715</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>127635</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>108585</xdr:rowOff>
@@ -46075,13 +46087,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>192405</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>312420</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -46113,13 +46125,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
       <xdr:row>88</xdr:row>
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>584835</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
@@ -46151,13 +46163,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>177165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>139065</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>89535</xdr:rowOff>
@@ -46189,13 +46201,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>203835</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -46557,7 +46569,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5">
         <v>2.1877294251263</v>
@@ -46599,7 +46611,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="5">
         <v>1.32397503582887</v>
@@ -46641,7 +46653,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5">
         <v>1.3077318896824699</v>
@@ -46683,7 +46695,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5">
         <v>2.1693958595572602</v>
@@ -46725,7 +46737,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="31">
         <v>1.57422422167948</v>
@@ -46767,7 +46779,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5">
         <v>1.1812082633028</v>
@@ -46809,7 +46821,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6">
         <v>0.80859807945185402</v>
@@ -46881,7 +46893,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" s="5">
         <v>1.49932904478425</v>
@@ -46904,7 +46916,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" s="5">
         <v>1.1773740554885099</v>
@@ -46927,7 +46939,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="5">
         <v>1.0062499424026501</v>
@@ -46950,7 +46962,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="5">
         <v>1.88871548942613</v>
@@ -46973,7 +46985,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18" s="31">
         <v>1.8348553138688299</v>
@@ -46996,7 +47008,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" s="6">
         <v>0.77555417160969797</v>
@@ -47019,7 +47031,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B20" s="5">
         <v>1.13570426691043</v>
@@ -47071,7 +47083,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="5">
         <v>1.05312198074008</v>
@@ -47094,7 +47106,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" s="6">
         <v>0.96447744969623705</v>
@@ -47117,7 +47129,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="5">
         <v>1.0170677163786801</v>
@@ -47140,7 +47152,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="6">
         <v>0.96859119932537396</v>
@@ -47163,7 +47175,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B27" s="34">
         <v>0.966529928734157</v>
@@ -47186,7 +47198,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="6">
         <v>0.99592174060442495</v>
@@ -47209,7 +47221,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B29" s="6">
         <v>0.93991290924357196</v>
@@ -47251,7 +47263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15CC4C3-E8D9-4F2F-B205-014F15A76EA5}">
-  <dimension ref="A3:H92"/>
+  <dimension ref="A3:K92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -47259,12 +47271,12 @@
     <col min="5" max="5" width="10.28515625" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>17</v>
@@ -47287,10 +47299,19 @@
       <c r="H3" s="9" t="s">
         <v>1</v>
       </c>
+      <c r="I3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -47313,10 +47334,19 @@
       <c r="H4" s="11">
         <v>10.97452421</v>
       </c>
+      <c r="I4" s="6">
+        <v>1.003934430437827E-2</v>
+      </c>
+      <c r="J4" s="6">
+        <v>6.0180800000000007E-2</v>
+      </c>
+      <c r="K4" s="6">
+        <v>2.45715E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9">
         <v>2</v>
@@ -47339,10 +47369,19 @@
       <c r="H5" s="11">
         <v>12.33049707</v>
       </c>
+      <c r="I5" s="6">
+        <v>2.2338385851655443E-2</v>
+      </c>
+      <c r="J5" s="6">
+        <v>3.6531200000000014E-2</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1.7498300000000022E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9">
         <v>3</v>
@@ -47363,10 +47402,19 @@
         <v>2.2839999999999998</v>
       </c>
       <c r="H6" s="11"/>
+      <c r="I6" s="6">
+        <v>9.8099758295017991E-3</v>
+      </c>
+      <c r="J6" s="6">
+        <v>3.28928E-2</v>
+      </c>
+      <c r="K6" s="6">
+        <v>2.1034899999999995E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="9">
         <v>4</v>
@@ -47389,10 +47437,19 @@
       <c r="H7" s="11">
         <v>4.9671491120000004</v>
       </c>
+      <c r="I7" s="6">
+        <v>1.031870116219955E-2</v>
+      </c>
+      <c r="J7" s="6">
+        <v>3.28928E-2</v>
+      </c>
+      <c r="K7" s="6">
+        <v>2.9876399999999997E-2</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="9">
         <v>5</v>
@@ -47415,10 +47472,19 @@
       <c r="H8" s="11">
         <v>8.8903534999999998</v>
       </c>
+      <c r="I8" s="6">
+        <v>6.2101564483107649E-3</v>
+      </c>
+      <c r="J8" s="6">
+        <v>3.4711999999999993E-2</v>
+      </c>
+      <c r="K8" s="6">
+        <v>2.6339799999999997E-2</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="9">
         <v>6</v>
@@ -47439,10 +47505,19 @@
         <v>2.4729999999999999</v>
       </c>
       <c r="H9" s="11"/>
+      <c r="I9" s="6">
+        <v>5.2426659536415413E-3</v>
+      </c>
+      <c r="J9" s="6">
+        <v>8.9288000000000034E-2</v>
+      </c>
+      <c r="K9" s="6">
+        <v>2.8108099999999997E-2</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="9">
         <v>7</v>
@@ -47463,10 +47538,19 @@
         <v>2.3140000000000001</v>
       </c>
       <c r="H10" s="11"/>
+      <c r="I10" s="6">
+        <v>3.2996877945532998E-3</v>
+      </c>
+      <c r="J10" s="6">
+        <v>3.8350400000000007E-2</v>
+      </c>
+      <c r="K10" s="6">
+        <v>2.8108099999999997E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" s="9">
         <v>8</v>
@@ -47487,10 +47571,19 @@
         <v>2.4020000000000001</v>
       </c>
       <c r="H11" s="11"/>
+      <c r="I11" s="6">
+        <v>2.600539216633088E-3</v>
+      </c>
+      <c r="J11" s="6">
+        <v>3.4711999999999993E-2</v>
+      </c>
+      <c r="K11" s="6">
+        <v>2.9876399999999997E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" s="9">
         <v>9</v>
@@ -47511,10 +47604,19 @@
         <v>2.278</v>
       </c>
       <c r="H12" s="11"/>
+      <c r="I12" s="6">
+        <v>2.618500653426792E-3</v>
+      </c>
+      <c r="J12" s="6">
+        <v>4.01696E-2</v>
+      </c>
+      <c r="K12" s="6">
+        <v>2.4571499999999996E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="9">
         <v>10</v>
@@ -47535,10 +47637,19 @@
         <v>2.2730000000000001</v>
       </c>
       <c r="H13" s="11"/>
+      <c r="I13" s="6">
+        <v>4.3689279273505278E-3</v>
+      </c>
+      <c r="J13" s="6">
+        <v>3.8350400000000007E-2</v>
+      </c>
+      <c r="K13" s="6">
+        <v>2.8108099999999997E-2</v>
+      </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" s="9">
         <v>11</v>
@@ -47559,10 +47670,19 @@
         <v>2.3010000000000002</v>
       </c>
       <c r="H14" s="11"/>
+      <c r="I14" s="6">
+        <v>3.1173927792587626E-3</v>
+      </c>
+      <c r="J14" s="6">
+        <v>3.28928E-2</v>
+      </c>
+      <c r="K14" s="6">
+        <v>2.6339799999999997E-2</v>
+      </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="9">
         <v>12</v>
@@ -47585,10 +47705,19 @@
       <c r="H15" s="11">
         <v>3.2415982130000001</v>
       </c>
+      <c r="I15" s="6">
+        <v>2.5711583887521052E-3</v>
+      </c>
+      <c r="J15" s="6">
+        <v>3.6531200000000014E-2</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1.9266599999999995E-2</v>
+      </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" s="9">
         <v>13</v>
@@ -47609,10 +47738,19 @@
         <v>2.3079999999999998</v>
       </c>
       <c r="H16" s="11"/>
+      <c r="I16" s="6">
+        <v>2.600539216633088E-3</v>
+      </c>
+      <c r="J16" s="6">
+        <v>3.4711999999999993E-2</v>
+      </c>
+      <c r="K16" s="6">
+        <v>2.1034899999999995E-2</v>
+      </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" s="9">
         <v>14</v>
@@ -47633,10 +47771,19 @@
         <v>2.214</v>
       </c>
       <c r="H17" s="11"/>
+      <c r="I17" s="6">
+        <v>2.2886277341208801E-3</v>
+      </c>
+      <c r="J17" s="6">
+        <v>3.8350400000000007E-2</v>
+      </c>
+      <c r="K17" s="6">
+        <v>2.2803199999999996E-2</v>
+      </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="12">
         <v>15</v>
@@ -47659,10 +47806,13 @@
       <c r="H18" s="14">
         <v>3.3278897669999998</v>
       </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19" s="12">
         <v>16</v>
@@ -47685,10 +47835,13 @@
       <c r="H19" s="14">
         <v>6.6628506349999999</v>
       </c>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20" s="12">
         <v>17</v>
@@ -47711,10 +47864,13 @@
       <c r="H20" s="14">
         <v>12.04121088</v>
       </c>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" s="12">
         <v>18</v>
@@ -47735,10 +47891,13 @@
         <v>2.7519999999999998</v>
       </c>
       <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" s="12">
         <v>19</v>
@@ -47761,10 +47920,13 @@
       <c r="H22" s="14">
         <v>8.058197302</v>
       </c>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" s="12">
         <v>20</v>
@@ -47785,10 +47947,13 @@
         <v>3.0089999999999999</v>
       </c>
       <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" s="12">
         <v>21</v>
@@ -47809,10 +47974,13 @@
         <v>2.7839999999999998</v>
       </c>
       <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" s="12">
         <v>22</v>
@@ -47835,10 +48003,13 @@
       <c r="H25" s="14">
         <v>5.0565465879999998</v>
       </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26" s="12">
         <v>23</v>
@@ -47861,10 +48032,13 @@
       <c r="H26" s="14">
         <v>3.736428037</v>
       </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" s="12">
         <v>24</v>
@@ -47885,10 +48059,13 @@
         <v>2.8039999999999998</v>
       </c>
       <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28" s="12">
         <v>25</v>
@@ -47909,10 +48086,13 @@
         <v>2.8639999999999999</v>
       </c>
       <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29" s="12">
         <v>26</v>
@@ -47935,10 +48115,13 @@
       <c r="H29" s="14">
         <v>2.771444281</v>
       </c>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" s="12">
         <v>27</v>
@@ -47959,10 +48142,13 @@
         <v>2.7690000000000001</v>
       </c>
       <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31" s="12">
         <v>28</v>
@@ -47983,10 +48169,13 @@
         <v>2.7410000000000001</v>
       </c>
       <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B32" s="12">
         <v>29</v>
@@ -48007,10 +48196,13 @@
         <v>2.7519999999999998</v>
       </c>
       <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33" s="12">
         <v>30</v>
@@ -48031,10 +48223,13 @@
         <v>2.7389999999999999</v>
       </c>
       <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34" s="15">
         <v>31</v>
@@ -48057,10 +48252,13 @@
       <c r="H34" s="17">
         <v>4.5952285179999999</v>
       </c>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" s="15">
         <v>32</v>
@@ -48083,10 +48281,13 @@
       <c r="H35" s="17">
         <v>10.93014432</v>
       </c>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" s="15">
         <v>33</v>
@@ -48107,10 +48308,13 @@
         <v>2.7010000000000001</v>
       </c>
       <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B37" s="15">
         <v>34</v>
@@ -48133,10 +48337,13 @@
       <c r="H37" s="17">
         <v>8.9789966309999993</v>
       </c>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B38" s="15">
         <v>35</v>
@@ -48157,10 +48364,13 @@
         <v>2.831</v>
       </c>
       <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B39" s="15">
         <v>36</v>
@@ -48181,10 +48391,13 @@
         <v>2.7629999999999999</v>
       </c>
       <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B40" s="15">
         <v>37</v>
@@ -48207,10 +48420,13 @@
       <c r="H40" s="17">
         <v>4.599424687</v>
       </c>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B41" s="15">
         <v>38</v>
@@ -48231,10 +48447,13 @@
         <v>2.7469999999999999</v>
       </c>
       <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B42" s="15">
         <v>39</v>
@@ -48255,10 +48474,13 @@
         <v>2.7410000000000001</v>
       </c>
       <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B43" s="15">
         <v>40</v>
@@ -48279,10 +48501,13 @@
         <v>2.7749999999999999</v>
       </c>
       <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B44" s="15">
         <v>41</v>
@@ -48303,10 +48528,13 @@
         <v>2.7330000000000001</v>
       </c>
       <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B45" s="15">
         <v>42</v>
@@ -48329,10 +48557,13 @@
       <c r="H45" s="17">
         <v>3.2584248140000001</v>
       </c>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B46" s="15">
         <v>43</v>
@@ -48353,10 +48584,13 @@
         <v>2.7850000000000001</v>
       </c>
       <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47" s="18">
         <v>44</v>
@@ -48379,10 +48613,13 @@
       <c r="H47" s="20">
         <v>8.3572964289999998</v>
       </c>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48" s="18">
         <v>45</v>
@@ -48405,10 +48642,13 @@
       <c r="H48" s="20">
         <v>24.660150940000001</v>
       </c>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49" s="18">
         <v>46</v>
@@ -48431,10 +48671,13 @@
       <c r="H49" s="20">
         <v>16.60466516</v>
       </c>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B50" s="18">
         <v>47</v>
@@ -48457,10 +48700,13 @@
       <c r="H50" s="20">
         <v>10.359493649999999</v>
       </c>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B51" s="18">
         <v>48</v>
@@ -48481,10 +48727,13 @@
         <v>2.0779999999999998</v>
       </c>
       <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B52" s="18">
         <v>49</v>
@@ -48507,10 +48756,13 @@
       <c r="H52" s="20">
         <v>9.2838971560000001</v>
       </c>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B53" s="18">
         <v>50</v>
@@ -48531,10 +48783,13 @@
         <v>2.1720000000000002</v>
       </c>
       <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54" s="18">
         <v>51</v>
@@ -48555,10 +48810,13 @@
         <v>2.3029999999999999</v>
       </c>
       <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B55" s="18">
         <v>52</v>
@@ -48579,10 +48837,13 @@
         <v>2.2890000000000001</v>
       </c>
       <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B56" s="18">
         <v>53</v>
@@ -48605,10 +48866,13 @@
       <c r="H56" s="20">
         <v>5.254678427</v>
       </c>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B57" s="18">
         <v>54</v>
@@ -48629,10 +48893,13 @@
         <v>2.2829999999999999</v>
       </c>
       <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58" s="18">
         <v>55</v>
@@ -48653,10 +48920,13 @@
         <v>2.202</v>
       </c>
       <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B59" s="21">
         <v>56</v>
@@ -48679,10 +48949,19 @@
       <c r="H59" s="23">
         <v>5.3161272320000004</v>
       </c>
+      <c r="I59" s="5">
+        <v>8.0744786331715737E-3</v>
+      </c>
+      <c r="J59" s="5">
+        <v>2.9254399999999986E-2</v>
+      </c>
+      <c r="K59" s="5">
+        <v>2.2803199999999996E-2</v>
+      </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B60" s="21">
         <v>57</v>
@@ -48705,10 +48984,19 @@
       <c r="H60" s="23">
         <v>20.72610796</v>
       </c>
+      <c r="I60" s="5">
+        <v>2.3321471582393793E-2</v>
+      </c>
+      <c r="J60" s="5">
+        <v>5.47232E-2</v>
+      </c>
+      <c r="K60" s="5">
+        <v>1.9266599999999995E-2</v>
+      </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B61" s="21">
         <v>58</v>
@@ -48729,10 +49017,19 @@
         <v>2.5630000000000002</v>
       </c>
       <c r="H61" s="23"/>
+      <c r="I61" s="5">
+        <v>1.9203510472240316E-2</v>
+      </c>
+      <c r="J61" s="5">
+        <v>3.28928E-2</v>
+      </c>
+      <c r="K61" s="5">
+        <v>2.2803199999999996E-2</v>
+      </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B62" s="21">
         <v>59</v>
@@ -48755,10 +49052,19 @@
       <c r="H62" s="23">
         <v>11.66797622</v>
       </c>
+      <c r="I62" s="5">
+        <v>1.15146880608244E-2</v>
+      </c>
+      <c r="J62" s="5">
+        <v>3.4711999999999993E-2</v>
+      </c>
+      <c r="K62" s="5">
+        <v>2.2803199999999996E-2</v>
+      </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B63" s="21">
         <v>60</v>
@@ -48779,10 +49085,19 @@
         <v>2.6960000000000002</v>
       </c>
       <c r="H63" s="23"/>
+      <c r="I63" s="5">
+        <v>9.856082656835876E-3</v>
+      </c>
+      <c r="J63" s="5">
+        <v>4.5627200000000007E-2</v>
+      </c>
+      <c r="K63" s="5">
+        <v>2.1034899999999995E-2</v>
+      </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B64" s="21">
         <v>61</v>
@@ -48805,10 +49120,19 @@
       <c r="H64" s="23">
         <v>6.6757924820000003</v>
       </c>
+      <c r="I64" s="5">
+        <v>1.16917712529308E-2</v>
+      </c>
+      <c r="J64" s="5">
+        <v>7.109600000000002E-2</v>
+      </c>
+      <c r="K64" s="5">
+        <v>2.1034899999999995E-2</v>
+      </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B65" s="21">
         <v>62</v>
@@ -48829,10 +49153,19 @@
         <v>2.742</v>
       </c>
       <c r="H65" s="23"/>
+      <c r="I65" s="5">
+        <v>1.2283480760895546E-2</v>
+      </c>
+      <c r="J65" s="5">
+        <v>8.2011200000000006E-2</v>
+      </c>
+      <c r="K65" s="5">
+        <v>1.7498300000000022E-2</v>
+      </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B66" s="21">
         <v>63</v>
@@ -48853,10 +49186,19 @@
         <v>2.7610000000000001</v>
       </c>
       <c r="H66" s="23"/>
+      <c r="I66" s="5">
+        <v>8.7555621153478178E-3</v>
+      </c>
+      <c r="J66" s="5">
+        <v>4.1988800000000021E-2</v>
+      </c>
+      <c r="K66" s="5">
+        <v>2.4571499999999996E-2</v>
+      </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B67" s="21">
         <v>64</v>
@@ -48877,10 +49219,19 @@
         <v>2.8210000000000002</v>
       </c>
       <c r="H67" s="23"/>
+      <c r="I67" s="5">
+        <v>5.741883910742567E-3</v>
+      </c>
+      <c r="J67" s="5">
+        <v>2.9254399999999986E-2</v>
+      </c>
+      <c r="K67" s="5">
+        <v>2.4571499999999996E-2</v>
+      </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" s="21">
         <v>65</v>
@@ -48903,10 +49254,19 @@
       <c r="H68" s="23">
         <v>5.6309098449999997</v>
       </c>
+      <c r="I68" s="5">
+        <v>4.5804950914437453E-3</v>
+      </c>
+      <c r="J68" s="5">
+        <v>2.7435199999999993E-2</v>
+      </c>
+      <c r="K68" s="5">
+        <v>2.6339799999999997E-2</v>
+      </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" s="21">
         <v>66</v>
@@ -48927,10 +49287,19 @@
         <v>2.7559999999999998</v>
       </c>
       <c r="H69" s="23"/>
+      <c r="I69" s="5">
+        <v>4.0576794789688791E-3</v>
+      </c>
+      <c r="J69" s="5">
+        <v>4.3808000000000014E-2</v>
+      </c>
+      <c r="K69" s="5">
+        <v>2.1034899999999995E-2</v>
+      </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" s="21">
         <v>67</v>
@@ -48951,10 +49320,19 @@
         <v>2.883</v>
       </c>
       <c r="H70" s="23"/>
+      <c r="I70" s="5">
+        <v>3.3758505307597045E-3</v>
+      </c>
+      <c r="J70" s="5">
+        <v>2.7435199999999993E-2</v>
+      </c>
+      <c r="K70" s="5">
+        <v>2.2803199999999996E-2</v>
+      </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B71" s="21">
         <v>68</v>
@@ -48975,10 +49353,19 @@
         <v>2.84</v>
       </c>
       <c r="H71" s="23"/>
+      <c r="I71" s="5">
+        <v>3.4794954752049401E-3</v>
+      </c>
+      <c r="J71" s="5">
+        <v>3.1073600000000007E-2</v>
+      </c>
+      <c r="K71" s="5">
+        <v>2.4571499999999996E-2</v>
+      </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B72" s="24">
         <v>69</v>
@@ -49001,10 +49388,13 @@
       <c r="H72" s="26">
         <v>3.6469399779999998</v>
       </c>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B73" s="24">
         <v>70</v>
@@ -49025,10 +49415,13 @@
         <v>3.0289999999999999</v>
       </c>
       <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B74" s="24">
         <v>71</v>
@@ -49051,10 +49444,13 @@
       <c r="H74" s="26">
         <v>2.38341665</v>
       </c>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B75" s="24">
         <v>72</v>
@@ -49075,10 +49471,13 @@
         <v>2.976</v>
       </c>
       <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B76" s="24">
         <v>73</v>
@@ -49101,10 +49500,13 @@
       <c r="H76" s="26">
         <v>2.1756635950000001</v>
       </c>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B77" s="24">
         <v>74</v>
@@ -49125,10 +49527,13 @@
         <v>3.0539999999999998</v>
       </c>
       <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B78" s="24">
         <v>75</v>
@@ -49149,10 +49554,13 @@
         <v>3.0379999999999998</v>
       </c>
       <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B79" s="24">
         <v>76</v>
@@ -49175,10 +49583,13 @@
       <c r="H79" s="26">
         <v>4.7777531050000004</v>
       </c>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B80" s="24">
         <v>77</v>
@@ -49199,10 +49610,13 @@
         <v>3.1509999999999998</v>
       </c>
       <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B81" s="24">
         <v>78</v>
@@ -49225,10 +49639,13 @@
       <c r="H81" s="26">
         <v>4.9322235059999997</v>
       </c>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B82" s="24">
         <v>79</v>
@@ -49249,10 +49666,13 @@
         <v>3.5510000000000002</v>
       </c>
       <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26"/>
+      <c r="K82" s="26"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B83" s="9">
         <v>85</v>
@@ -49275,10 +49695,13 @@
       <c r="H83" s="27">
         <v>5.5154976969999998</v>
       </c>
+      <c r="I83" s="27"/>
+      <c r="J83" s="27"/>
+      <c r="K83" s="27"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B84" s="9">
         <v>86</v>
@@ -49299,10 +49722,13 @@
         <v>3.0539999999999998</v>
       </c>
       <c r="H84" s="27"/>
+      <c r="I84" s="27"/>
+      <c r="J84" s="27"/>
+      <c r="K84" s="27"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B85" s="9">
         <v>87</v>
@@ -49325,10 +49751,13 @@
       <c r="H85" s="27">
         <v>3.927531906</v>
       </c>
+      <c r="I85" s="27"/>
+      <c r="J85" s="27"/>
+      <c r="K85" s="27"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B86" s="9">
         <v>88</v>
@@ -49349,10 +49778,13 @@
         <v>2.6160000000000001</v>
       </c>
       <c r="H86" s="27"/>
+      <c r="I86" s="27"/>
+      <c r="J86" s="27"/>
+      <c r="K86" s="27"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B87" s="9">
         <v>89</v>
@@ -49375,10 +49807,13 @@
       <c r="H87" s="27">
         <v>15.122709800000001</v>
       </c>
+      <c r="I87" s="27"/>
+      <c r="J87" s="27"/>
+      <c r="K87" s="27"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B88" s="9">
         <v>90</v>
@@ -49399,10 +49834,13 @@
         <v>2.9359999999999999</v>
       </c>
       <c r="H88" s="27"/>
+      <c r="I88" s="27"/>
+      <c r="J88" s="27"/>
+      <c r="K88" s="27"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B89" s="9">
         <v>91</v>
@@ -49425,10 +49863,13 @@
       <c r="H89" s="27">
         <v>17.196570690000001</v>
       </c>
+      <c r="I89" s="27"/>
+      <c r="J89" s="27"/>
+      <c r="K89" s="27"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B90" s="9">
         <v>92</v>
@@ -49451,10 +49892,13 @@
       <c r="H90" s="27">
         <v>9.5060401779999992</v>
       </c>
+      <c r="I90" s="27"/>
+      <c r="J90" s="27"/>
+      <c r="K90" s="27"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B91" s="9">
         <v>93</v>
@@ -49477,10 +49921,13 @@
       <c r="H91" s="27">
         <v>6.3675166709999997</v>
       </c>
+      <c r="I91" s="27"/>
+      <c r="J91" s="27"/>
+      <c r="K91" s="27"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B92" s="9">
         <v>94</v>
@@ -49501,6 +49948,9 @@
         <v>2.4969999999999999</v>
       </c>
       <c r="H92" s="27"/>
+      <c r="I92" s="27"/>
+      <c r="J92" s="27"/>
+      <c r="K92" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
+++ b/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\experiments\HI_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B6D383-5643-4A62-8144-24F1BEF0648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7460BE-8AC0-4B00-BD8D-581DBB265705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="33">
   <si>
     <t>DOC (mg/L)</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t xml:space="preserve">Experiment Hysteresis </t>
-  </si>
-  <si>
-    <t>Experiment 1</t>
   </si>
   <si>
     <t>Experiment 2</t>
@@ -70,12 +67,6 @@
   </si>
   <si>
     <t xml:space="preserve">SSC (mg/L) </t>
-  </si>
-  <si>
-    <t>Langlois</t>
-  </si>
-  <si>
-    <t>Lawler</t>
   </si>
   <si>
     <t>SSC (mg/L)</t>
@@ -120,9 +111,6 @@
     <t>Peak Constituent (mg/L)</t>
   </si>
   <si>
-    <t>Log Langlois</t>
-  </si>
-  <si>
     <t>Largest moved size</t>
   </si>
   <si>
@@ -146,15 +134,18 @@
   <si>
     <t>SRP (mg/L)</t>
   </si>
+  <si>
+    <t>TP (mg/L)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -251,12 +242,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -269,9 +257,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -349,13 +334,35 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -537,7 +544,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$5:$F$9</c:f>
+              <c:f>Sheet1!$C$5:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -561,7 +568,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -929,303 +936,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.18188667782560905"/>
-                  <c:y val="-0.13955211302208961"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$5:$C$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.33999360813627283</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.12187979635445149</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11651871435007208</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.33633880694037765</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.19706659035014132</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BB9C-4AD3-B6EE-0FADA5E5F3ED}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.22361897589465474"/>
-                  <c:y val="-0.21326621057613701"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$5:$D$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.71803227014055304</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.24125163857843901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.39340714771465102</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.79163162608253801</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.44150780994259298</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BB9C-4AD3-B6EE-0FADA5E5F3ED}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1272,8 +987,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="6.5270014092743342E-2"/>
-                  <c:y val="-0.19397831418613656"/>
+                  <c:x val="-4.0977910056006664E-2"/>
+                  <c:y val="-9.2061439880202239E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1313,7 +1028,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
+              <c:f>Sheet1!$J$5:$J$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1337,7 +1052,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1622,15 +1337,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -1816,303 +1523,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.6536149268993618E-2"/>
-                  <c:y val="2.3817391678499205E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$14:$C$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.17589695416394432</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.0914461506453946E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.7058685170807499E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.27616654199898055</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.26360182397461063</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E4FB-42AF-B79B-D5E2D924DE5B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.23764732726065696"/>
-                  <c:y val="-2.234972677595631E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$14:$D$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.77642606785996804</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.18229454485882499</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.240947268722355</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.88806250457032299</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.92716260893139602</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-E4FB-42AF-B79B-D5E2D924DE5B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2159,8 +1574,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.17974949422554479"/>
-                  <c:y val="0.17622262381136783"/>
+                  <c:x val="9.9486914983042574E-2"/>
+                  <c:y val="-0.19075746396164034"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -2200,7 +1615,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
+              <c:f>Sheet1!$J$5:$J$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2224,7 +1639,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$14:$E$18</c:f>
+              <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2509,15 +1924,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -2703,303 +2110,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-8.5891543619087879E-2"/>
-                  <c:y val="-9.8173056236822862E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$23:$C$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2.2478677447762781E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1.5707922076061909E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3498692163067999E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-1.3859481295871032E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-1.4784693437961027E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2837-4188-8729-C7C0C594020E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.30811384360939409"/>
-                  <c:y val="-0.20110451357514739"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$23:$D$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.29004509914582</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.88020825662958402</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.47015675471698098</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.50732452729004396</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.92976462887333999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-2837-4188-8729-C7C0C594020E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3087,7 +2202,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
+              <c:f>Sheet1!$J$5:$J$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3111,7 +2226,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$23:$E$27</c:f>
+              <c:f>Sheet1!$B$23:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3396,15 +2511,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -3505,6 +2612,47 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>SS</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>HI to POC</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> HI</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3544,7 +2692,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -3587,7 +2735,12 @@
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:noFill/>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -3617,7 +2770,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3641,24 +2794,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$F$5:$F$9</c:f>
+              <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>167.04416760000001</c:v>
+                  <c:v>0.262211557214444</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5418607</c:v>
+                  <c:v>0.15997395020695501</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>174.6761387</c:v>
+                  <c:v>-2.5566841037180299E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>287.8289474</c:v>
+                  <c:v>0.62020718230999505</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>243.34662650000001</c:v>
+                  <c:v>0.78199948801270402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3764,7 +2917,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3978,8 +3131,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.689204790622849E-2"/>
-                  <c:y val="-3.7657682708157364E-2"/>
+                  <c:x val="-0.18303526383781843"/>
+                  <c:y val="-8.635623441843937E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -4019,7 +3172,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -4043,24 +3196,24 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$14:$E$18</c:f>
+              <c:f>Sheet1!$C$5:$C$9</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.262211557214444</c:v>
+                  <c:v>167.04416760000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15997395020695501</c:v>
+                  <c:v>162.5418607</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.5566841037180299E-3</c:v>
+                  <c:v>174.6761387</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.62020718230999505</c:v>
+                  <c:v>287.8289474</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.78199948801270402</c:v>
+                  <c:v>243.34662650000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4226,7 +3379,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8006,7 +7159,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$14:$F$18</c:f>
+              <c:f>Sheet1!$C$14:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -8030,7 +7183,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -13938,7 +13091,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$F$23:$F$27</c:f>
+              <c:f>Sheet1!$C$23:$C$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -13962,7 +13115,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -19186,303 +18339,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.18188667782560905"/>
-                  <c:y val="-0.13955211302208961"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$5:$C$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.33999360813627283</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.12187979635445149</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11651871435007208</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.33633880694037765</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.19706659035014132</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D4A9-4C14-9726-1168DCD6B822}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.22361897589465474"/>
-                  <c:y val="-0.21326621057613701"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$5:$D$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.71803227014055304</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.24125163857843901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.39340714771465102</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.79163162608253801</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.44150780994259298</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D4A9-4C14-9726-1168DCD6B822}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -19529,8 +18390,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="6.5270014092743342E-2"/>
-                  <c:y val="-0.19397831418613656"/>
+                  <c:x val="-0.25535005298777314"/>
+                  <c:y val="-0.13613537488583957"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -19570,7 +18431,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -19594,7 +18455,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -19879,15 +18740,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -20062,303 +18915,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.6536149268993618E-2"/>
-                  <c:y val="2.3817391678499205E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$14:$C$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.17589695416394432</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.0914461506453946E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.7058685170807499E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.27616654199898055</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.26360182397461063</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0839-487E-A311-BCCCAA7A366F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.23764732726065696"/>
-                  <c:y val="-2.234972677595631E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$14:$D$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.77642606785996804</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.18229454485882499</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.240947268722355</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.88806250457032299</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.92716260893139602</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0839-487E-A311-BCCCAA7A366F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -20446,7 +19007,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -20470,7 +19031,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$14:$E$18</c:f>
+              <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -20755,15 +19316,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -20938,303 +19491,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.6536149268993618E-2"/>
-                  <c:y val="2.3817391678499205E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$23:$C$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2.2478677447762781E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1.5707922076061909E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3498692163067999E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-1.3859481295871032E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-1.4784693437961027E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-820F-4F8C-BA92-5CCDAB8D9CC8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.23764732726065696"/>
-                  <c:y val="-2.234972677595631E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>22.75</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.992000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21.641999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21.291</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.274999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$23:$D$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.29004509914582</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.88020825662958402</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.47015675471698098</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.50732452729004396</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.92976462887333999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-820F-4F8C-BA92-5CCDAB8D9CC8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -21281,8 +19542,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="5.1241662726741195E-2"/>
-                  <c:y val="-0.15205412847984165"/>
+                  <c:x val="-0.24282458767050835"/>
+                  <c:y val="-8.7987755560450395E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -21322,7 +19583,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$I$5:$I$9</c:f>
+              <c:f>Sheet1!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -21346,7 +19607,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$23:$E$27</c:f>
+              <c:f>Sheet1!$B$23:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -21631,15 +19892,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -21812,308 +20065,26 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20131102733533501"/>
+          <c:y val="0.20525062473719646"/>
+          <c:w val="0.6855728393477023"/>
+          <c:h val="0.42244042937473991"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.18188667782560905"/>
-                  <c:y val="-0.13955211302208961"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>71.428571428571431</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.272727272727266</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.363636363636367</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.826086956521742</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$5:$C$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.33999360813627283</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.12187979635445149</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11651871435007208</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.33633880694037765</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.19706659035014132</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E8E6-4FE1-8321-4E3B373DD93E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.22361897589465474"/>
-                  <c:y val="-0.21326621057613701"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>71.428571428571431</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.272727272727266</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.363636363636367</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.826086956521742</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$5:$D$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.71803227014055304</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.24125163857843901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.39340714771465102</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.79163162608253801</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.44150780994259298</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-E8E6-4FE1-8321-4E3B373DD93E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -22160,8 +20131,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="6.5270014092743342E-2"/>
-                  <c:y val="-0.19397831418613656"/>
+                  <c:x val="-0.19714173298657231"/>
+                  <c:y val="1.942949021009035E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -22201,7 +20172,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
+              <c:f>Sheet1!$I$5:$I$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -22225,7 +20196,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$5:$E$9</c:f>
+              <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -22510,15 +20481,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -22704,303 +20667,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.6536149268993618E-2"/>
-                  <c:y val="2.3817391678499205E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>71.428571428571431</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.272727272727266</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.363636363636367</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.826086956521742</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$14:$C$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.17589695416394432</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.0914461506453946E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.7058685170807499E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.27616654199898055</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.26360182397461063</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BDA8-4C5B-9C96-7B3244B7219A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.23764732726065696"/>
-                  <c:y val="-2.234972677595631E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>71.428571428571431</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.272727272727266</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.363636363636367</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.826086956521742</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$14:$D$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.77642606785996804</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.18229454485882499</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.240947268722355</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.88806250457032299</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.92716260893139602</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BDA8-4C5B-9C96-7B3244B7219A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -23088,7 +20759,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
+              <c:f>Sheet1!$I$5:$I$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -23112,7 +20783,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$14:$E$18</c:f>
+              <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -23397,15 +21068,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -23591,303 +21254,11 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="2"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$B$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Langlois</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.6536149268993618E-2"/>
-                  <c:y val="2.3817391678499205E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$M$5:$M$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85.714285714285708</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>61.53846153846154</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>30.76923076923077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>33.333333333333329</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$23:$C$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2.2478677447762781E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-1.5707922076061909E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.3498692163067999E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-1.3859481295871032E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-1.4784693437961027E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-36BC-4E11-9BBF-19EC9EBC795B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$22</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Lawler</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.23764732726065696"/>
-                  <c:y val="-2.234972677595631E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>71.428571428571431</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.272727272727266</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36.363636363636367</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.826086956521742</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$D$23:$D$27</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.29004509914582</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.88020825662958402</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.47015675471698098</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.50732452729004396</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.92976462887333999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-36BC-4E11-9BBF-19EC9EBC795B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$22</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -23975,7 +21346,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$L$5:$L$9</c:f>
+              <c:f>Sheet1!$I$5:$I$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -23999,7 +21370,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$23:$E$27</c:f>
+              <c:f>Sheet1!$B$23:$B$27</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="5"/>
@@ -24284,15 +21655,7 @@
     <c:legend>
       <c:legendPos val="b"/>
       <c:legendEntry>
-        <c:idx val="3"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="4"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="5"/>
+        <c:idx val="1"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:layout>
@@ -44796,13 +42159,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>66674</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
@@ -44832,13 +42195,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>219074</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
@@ -44870,13 +42233,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>466724</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
@@ -44908,13 +42271,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>38099</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -44946,13 +42309,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>257174</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -44984,13 +42347,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>504824</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
@@ -45022,13 +42385,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>885825</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>28574</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
@@ -45060,13 +42423,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>247649</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -45098,13 +42461,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>495299</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -45136,13 +42499,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>47624</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
@@ -45174,13 +42537,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>266699</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
@@ -45212,13 +42575,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>314325</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>514349</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
@@ -45250,16 +42613,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>162036</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>17256</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1072739</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>40509</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -45286,16 +42649,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1156112</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>2240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1409699</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>919779</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>43422</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -46503,757 +43866,722 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
-    <col min="2" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>10</v>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="I4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
-        <v>2.1877294251263</v>
-      </c>
-      <c r="C5" s="5">
-        <f>LOG10(B5)</f>
-        <v>0.33999360813627283</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0.71803227014055304</v>
-      </c>
-      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.453436795025429</v>
       </c>
-      <c r="F5" s="8">
+      <c r="C5" s="6">
         <f>MAX('constituent correlations'!F4:F17)</f>
         <v>167.04416760000001</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="1">
+      <c r="F5" s="1">
         <f>MAX('constituent correlations'!D4:D17)</f>
         <v>22.75</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1">
         <v>128</v>
       </c>
-      <c r="L5" s="8">
+      <c r="I5" s="6">
         <v>71.428571428571431</v>
       </c>
-      <c r="M5" s="8">
+      <c r="J5" s="6">
         <v>85.714285714285708</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5">
-        <v>1.32397503582887</v>
-      </c>
-      <c r="C6" s="5">
-        <f t="shared" ref="C6:C11" si="0">LOG10(B6)</f>
-        <v>0.12187979635445149</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0.24125163857843901</v>
-      </c>
-      <c r="E6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.14144997157405101</v>
       </c>
-      <c r="F6" s="8">
+      <c r="C6" s="6">
         <f>MAX('constituent correlations'!F18:F33)</f>
         <v>162.5418607</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="1">
+      <c r="F6" s="1">
         <f>MAX('constituent correlations'!D18:D33)</f>
         <v>21.992000000000001</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1">
         <v>128</v>
       </c>
-      <c r="L6" s="8">
+      <c r="I6" s="6">
         <v>77.272727272727266</v>
       </c>
-      <c r="M6" s="8">
+      <c r="J6" s="6">
         <v>61.53846153846154</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1.3077318896824699</v>
-      </c>
-      <c r="C7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.11651871435007208</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0.39340714771465102</v>
-      </c>
-      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
         <v>0.13607881876945299</v>
       </c>
-      <c r="F7" s="8">
+      <c r="C7" s="6">
         <f>MAX('constituent correlations'!F34:F46)</f>
         <v>174.6761387</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="1">
+      <c r="F7" s="1">
         <f>MAX('constituent correlations'!D34:D46)</f>
         <v>21.641999999999999</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="G7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1">
         <v>90</v>
       </c>
-      <c r="L7" s="8">
+      <c r="I7" s="6">
         <v>36.363636363636367</v>
       </c>
-      <c r="M7" s="8">
+      <c r="J7" s="6">
         <v>30.76923076923077</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5">
-        <v>2.1693958595572602</v>
-      </c>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
-        <v>0.33633880694037765</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0.79163162608253801</v>
-      </c>
-      <c r="E8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.61769731984154397</v>
       </c>
-      <c r="F8" s="8">
+      <c r="C8" s="6">
         <f>MAX('constituent correlations'!F47:F58)</f>
         <v>287.8289474</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="1">
+      <c r="F8" s="1">
         <f>MAX('constituent correlations'!D47:D58)</f>
         <v>21.291</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="G8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1">
         <v>128</v>
       </c>
-      <c r="L8" s="8">
+      <c r="I8" s="6">
         <v>40</v>
       </c>
-      <c r="M8" s="8">
+      <c r="J8" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="31">
-        <v>1.57422422167948</v>
-      </c>
-      <c r="C9" s="31">
-        <f t="shared" si="0"/>
-        <v>0.19706659035014132</v>
-      </c>
-      <c r="D9" s="31">
-        <v>0.44150780994259298</v>
-      </c>
-      <c r="E9" s="31">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="29">
         <v>0.66455526442613699</v>
       </c>
-      <c r="F9" s="32">
+      <c r="C9" s="30">
         <f>MAX('constituent correlations'!F59:F71)</f>
         <v>243.34662650000001</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="1">
+      <c r="F9" s="28">
         <f>MAX('constituent correlations'!D59:D71)</f>
         <v>23.274999999999999</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="G9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="28">
         <v>64</v>
       </c>
-      <c r="L9" s="8">
+      <c r="I9" s="30">
         <v>47.826086956521742</v>
       </c>
-      <c r="M9" s="8">
+      <c r="J9" s="30">
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5">
-        <v>1.1812082633028</v>
-      </c>
-      <c r="C10" s="5">
-        <f t="shared" si="0"/>
-        <v>7.2326476469688039E-2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>19.897713037632499</v>
-      </c>
-      <c r="E10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
         <v>0.15353684539821699</v>
       </c>
-      <c r="F10" s="8">
+      <c r="C10" s="6">
         <f>MAX('constituent correlations'!F72:F82)</f>
         <v>44.890630100000003</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="8">
+      <c r="F10" s="6">
         <f>MAX('constituent correlations'!D72:D82)</f>
         <v>10.617000000000001</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="J10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="6">
-        <v>0.80859807945185402</v>
+        <v>28</v>
+      </c>
+      <c r="B11" s="5">
+        <v>-0.28559783552715301</v>
       </c>
       <c r="C11" s="6">
-        <f t="shared" si="0"/>
-        <v>-9.2267294519105064E-2</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-0.49644114829115799</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.28559783552715301</v>
-      </c>
-      <c r="F11" s="8">
         <f>MAX('constituent correlations'!F83:F92)</f>
         <v>240.01979539999999</v>
       </c>
-      <c r="G11" s="1">
-        <f>F10/F11</f>
+      <c r="D11" s="1">
+        <f>C10/C11</f>
         <v>0.18702886578662589</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="E11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="6">
         <f>MAX('constituent correlations'!D83:D92)</f>
         <v>9.3919999999999995</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="L12" s="1"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5">
-        <v>1.49932904478425</v>
-      </c>
-      <c r="C14" s="5">
-        <f>LOG10(B14)</f>
-        <v>0.17589695416394432</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.77642606785996804</v>
-      </c>
-      <c r="E14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4">
         <v>0.262211557214444</v>
       </c>
-      <c r="F14" s="8">
+      <c r="C14" s="6">
         <f>MAX('constituent correlations'!H4:H17)</f>
         <v>12.33049707</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="5">
-        <v>1.1773740554885099</v>
-      </c>
-      <c r="C15" s="5">
-        <f t="shared" ref="C15:C20" si="1">LOG10(B15)</f>
-        <v>7.0914461506453946E-2</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.18229454485882499</v>
-      </c>
-      <c r="E15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="4">
         <v>0.15997395020695501</v>
       </c>
-      <c r="F15" s="8">
+      <c r="C15" s="6">
         <f>MAX('constituent correlations'!H18:H33)</f>
         <v>12.04121088</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="5">
-        <v>1.0062499424026501</v>
-      </c>
-      <c r="C16" s="5">
-        <f t="shared" si="1"/>
-        <v>2.7058685170807499E-3</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.240947268722355</v>
-      </c>
-      <c r="E16" s="6">
         <v>-2.5566841037180299E-3</v>
       </c>
-      <c r="F16" s="8">
+      <c r="C16" s="6">
         <f>MAX('constituent correlations'!H34:H46)</f>
         <v>10.93014432</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1.88871548942613</v>
-      </c>
-      <c r="C17" s="5">
-        <f t="shared" si="1"/>
-        <v>0.27616654199898055</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.88806250457032299</v>
-      </c>
-      <c r="E17" s="5">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4">
         <v>0.62020718230999505</v>
       </c>
-      <c r="F17" s="8">
+      <c r="C17" s="6">
         <f>MAX('constituent correlations'!H47:H58)</f>
         <v>24.660150940000001</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="31">
-        <v>1.8348553138688299</v>
-      </c>
-      <c r="C18" s="31">
-        <f t="shared" si="1"/>
-        <v>0.26360182397461063</v>
-      </c>
-      <c r="D18" s="31">
-        <v>0.92716260893139602</v>
-      </c>
-      <c r="E18" s="31">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="29">
         <v>0.78199948801270402</v>
       </c>
-      <c r="F18" s="32">
+      <c r="C18" s="30">
         <f>MAX('constituent correlations'!H59:H71)</f>
         <v>20.72610796</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="6">
-        <v>0.77555417160969797</v>
+        <v>8</v>
+      </c>
+      <c r="B19" s="5">
+        <v>-0.501279910362319</v>
       </c>
       <c r="C19" s="6">
-        <f t="shared" si="1"/>
-        <v>-0.11038786179686137</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.97565062007097603</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.501279910362319</v>
-      </c>
-      <c r="F19" s="8">
         <f>MAX('constituent correlations'!H72:H82)</f>
         <v>4.9322235059999997</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="5">
-        <v>1.13570426691043</v>
-      </c>
-      <c r="C20" s="5">
-        <f t="shared" si="1"/>
-        <v>5.5265257458194293E-2</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.57558838807602997</v>
-      </c>
-      <c r="E20" s="5">
+        <v>28</v>
+      </c>
+      <c r="B20" s="4">
         <v>0.14455219387620799</v>
       </c>
-      <c r="F20" s="8">
+      <c r="C20" s="6">
         <f>MAX('constituent correlations'!H83:H92)</f>
         <v>17.196570690000001</v>
       </c>
-      <c r="G20" s="1">
-        <f>F19/F20</f>
+      <c r="D20" s="1">
+        <f>C19/C20</f>
         <v>0.28681436519597148</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="5">
-        <v>1.05312198074008</v>
-      </c>
-      <c r="C23" s="5">
-        <f>LOG10(B23)</f>
-        <v>2.2478677447762781E-2</v>
-      </c>
-      <c r="D23" s="33">
-        <v>0.29004509914582</v>
-      </c>
-      <c r="E23" s="5">
+        <v>3</v>
+      </c>
+      <c r="B23" s="4">
         <v>8.2872285708523799E-2</v>
       </c>
-      <c r="F23" s="1">
+      <c r="C23" s="1">
         <f>MAX('constituent correlations'!G4:G17)</f>
         <v>2.64</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6">
-        <v>0.96447744969623705</v>
-      </c>
-      <c r="C24" s="6">
-        <f t="shared" ref="C24:C29" si="2">LOG10(B24)</f>
-        <v>-1.5707922076061909E-2</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.88020825662958402</v>
-      </c>
-      <c r="E24" s="6">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5">
         <v>-0.120864394889326</v>
       </c>
-      <c r="F24" s="1">
+      <c r="C24" s="1">
         <f>MAX('constituent correlations'!G18:G33)</f>
         <v>3.0089999999999999</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1.0170677163786801</v>
-      </c>
-      <c r="C25" s="5">
-        <f t="shared" si="2"/>
-        <v>7.3498692163067999E-3</v>
-      </c>
-      <c r="D25" s="33">
-        <v>0.47015675471698098</v>
-      </c>
-      <c r="E25" s="5">
+        <v>5</v>
+      </c>
+      <c r="B25" s="4">
         <v>1.1974710137234199E-2</v>
       </c>
-      <c r="F25" s="1">
+      <c r="C25" s="1">
         <f>MAX('constituent correlations'!G34:G46)</f>
         <v>2.8980000000000001</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="6">
-        <v>0.96859119932537396</v>
-      </c>
-      <c r="C26" s="6">
-        <f t="shared" si="2"/>
-        <v>-1.3859481295871032E-2</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.50732452729004396</v>
-      </c>
-      <c r="E26" s="6">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5">
         <v>-9.3327819128066702E-2</v>
       </c>
-      <c r="F26" s="1">
+      <c r="C26" s="1">
         <f>MAX('constituent correlations'!G47:G58)</f>
         <v>2.3029999999999999</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="34">
-        <v>0.966529928734157</v>
-      </c>
-      <c r="C27" s="34">
-        <f t="shared" si="2"/>
-        <v>-1.4784693437961027E-2</v>
-      </c>
-      <c r="D27" s="35">
-        <v>-0.92976462887333999</v>
-      </c>
-      <c r="E27" s="34">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="31">
         <v>-7.3285474508812898E-2</v>
       </c>
-      <c r="F27" s="30">
+      <c r="C27" s="28">
         <f>MAX('constituent correlations'!G59:G71)</f>
         <v>2.883</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="6">
-        <v>0.99592174060442495</v>
+        <v>8</v>
+      </c>
+      <c r="B28" s="5">
+        <v>-8.6314057587169295E-3</v>
       </c>
       <c r="C28" s="6">
-        <f t="shared" si="2"/>
-        <v>-1.7747870371363919E-3</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-0.69333459331862701</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-8.6314057587169295E-3</v>
-      </c>
-      <c r="F28" s="8">
         <f>MAX('constituent correlations'!G72:G82)</f>
         <v>3.641</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="6">
-        <v>0.93991290924357196</v>
+        <v>28</v>
+      </c>
+      <c r="B29" s="4">
+        <v>4.5754279708113597E-2</v>
       </c>
       <c r="C29" s="6">
-        <f t="shared" si="2"/>
-        <v>-2.6912385535617193E-2</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-0.64143347885615298</v>
-      </c>
-      <c r="E29" s="5">
-        <v>4.5754279708113597E-2</v>
-      </c>
-      <c r="F29" s="8">
         <f>MAX('constituent correlations'!G83:G92)</f>
         <v>3.1349999999999998</v>
       </c>
-      <c r="G29" s="1">
-        <f>F28/F29</f>
+      <c r="D29" s="1">
+        <f>C28/C29</f>
         <v>1.1614035087719299</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="1"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="32">
+        <v>0.39025509275430098</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.2338385851655443E-2</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="35"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="35"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="35"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="29">
+        <v>0.54200255292126898</v>
+      </c>
+      <c r="C36" s="28">
+        <v>2.3321471582393793E-2</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="34"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="34"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="1" t="e">
+        <f>C37/C38</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="5">
+        <v>-0.26955872659063201</v>
+      </c>
+      <c r="C41" s="36">
+        <v>2.9876399999999997E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="34"/>
+      <c r="C42" s="36"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="34"/>
+      <c r="C43" s="36"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="34"/>
+      <c r="C44" s="36"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="29">
+        <v>2.6807256740673498E-3</v>
+      </c>
+      <c r="C45" s="37">
+        <v>2.6339799999999997E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="34"/>
+      <c r="C46" s="38"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="34"/>
+      <c r="C47" s="38"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="36"/>
+      <c r="C48" s="39"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="33">
+        <v>-0.33213619826679402</v>
+      </c>
+      <c r="C50" s="36">
+        <v>8.9288000000000034E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="40"/>
+      <c r="C51" s="36"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="40"/>
+      <c r="C52" s="36"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="36"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="41">
+        <v>-0.235823563048565</v>
+      </c>
+      <c r="C54" s="37">
+        <v>8.2011200000000006E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="34"/>
+      <c r="C55" s="38"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="34"/>
+      <c r="C56" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47275,2682 +44603,2682 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>35</v>
+      <c r="I3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>44775.498020833336</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <v>9.2750000000000004</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>97.69</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>167.04416760000001</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="9">
         <v>2.64</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="9">
         <v>10.97452421</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>1.003934430437827E-2</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>6.0180800000000007E-2</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>2.45715E-2</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>44775.498159722221</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <v>22.75</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>347.61</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <v>145.0786205</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="9">
         <v>2.3839999999999999</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="9">
         <v>12.33049707</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>2.2338385851655443E-2</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>3.6531200000000014E-2</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>1.7498300000000022E-2</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9">
+      <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="10">
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8">
         <v>44775.498287037037</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <v>19.25</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>191.85</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <v>76.137884869999993</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <v>2.2839999999999998</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="6">
+      <c r="H6" s="9"/>
+      <c r="I6" s="5">
         <v>9.8099758295017991E-3</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>3.28928E-2</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>2.1034899999999995E-2</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="9">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10">
+      <c r="C7" s="8">
         <v>44775.498402777775</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>16.100000000000001</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>176.97</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <v>47.967684929999997</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="9">
         <v>2.423</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="9">
         <v>4.9671491120000004</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>1.031870116219955E-2</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>3.28928E-2</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>2.9876399999999997E-2</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="8">
         <v>44775.498530092591</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <v>13.884</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>127.27</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <v>67.326074309999996</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <v>2.488</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <v>8.8903534999999998</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>6.2101564483107649E-3</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>3.4711999999999993E-2</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>2.6339799999999997E-2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="9">
+      <c r="A9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <v>44775.498657407406</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="9">
         <v>12.775</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <v>83.04</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="9">
         <v>61.268421920000002</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="9">
         <v>2.4729999999999999</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="6">
+      <c r="H9" s="9"/>
+      <c r="I9" s="5">
         <v>5.2426659536415413E-3</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>8.9288000000000034E-2</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>2.8108099999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="9">
+      <c r="A10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="8">
         <v>44775.498773148145</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <v>12.134</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>68.69</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>40.782355389999999</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <v>2.3140000000000001</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="6">
+      <c r="H10" s="9"/>
+      <c r="I10" s="5">
         <v>3.2996877945532998E-3</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>3.8350400000000007E-2</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>2.8108099999999997E-2</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="9">
+      <c r="A11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <v>44775.498900462961</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <v>11.959</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>62.04</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <v>43.350237200000002</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="9">
         <v>2.4020000000000001</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="6">
+      <c r="H11" s="9"/>
+      <c r="I11" s="5">
         <v>2.600539216633088E-3</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <v>3.4711999999999993E-2</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>2.9876399999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="9">
+      <c r="A12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="8">
         <v>44775.49900462963</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <v>11.959</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>61.07</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <v>37.341299480000004</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="9">
         <v>2.278</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="6">
+      <c r="H12" s="9"/>
+      <c r="I12" s="5">
         <v>2.618500653426792E-3</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>4.01696E-2</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>2.4571499999999996E-2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="9">
+      <c r="A13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="8">
         <v>44775.499120370368</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="9">
         <v>11.784000000000001</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <v>48.37</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="9">
         <v>22.213081039999999</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <v>2.2730000000000001</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="6">
+      <c r="H13" s="9"/>
+      <c r="I13" s="5">
         <v>4.3689279273505278E-3</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <v>3.8350400000000007E-2</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>2.8108099999999997E-2</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="9">
+      <c r="A14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="8">
         <v>44775.499236111114</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="9">
         <v>11.959</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <v>29.69</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <v>20.67311668</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <v>2.3010000000000002</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="6">
+      <c r="H14" s="9"/>
+      <c r="I14" s="5">
         <v>3.1173927792587626E-3</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>3.28928E-2</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>2.6339799999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="9">
+      <c r="A15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="8">
         <v>44775.499351851853</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="9">
         <v>11.667</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <v>28.69</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="9">
         <v>12.54810105</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="9">
         <v>2.3130000000000002</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="9">
         <v>3.2415982130000001</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>2.5711583887521052E-3</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>3.6531200000000014E-2</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>1.9266599999999995E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="9">
+      <c r="A16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="8">
         <v>44775.499456018515</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="9">
         <v>11.492000000000001</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <v>22.43</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="9">
         <v>10.726957670000001</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="9">
         <v>2.3079999999999998</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="6">
+      <c r="H16" s="9"/>
+      <c r="I16" s="5">
         <v>2.600539216633088E-3</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>3.4711999999999993E-2</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>2.1034899999999995E-2</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="9">
+      <c r="A17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="8">
         <v>44775.499583333331</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="9">
         <v>11.667</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <v>0</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="9">
         <v>6.5843621399999996</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="9">
         <v>2.214</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="6">
+      <c r="H17" s="9"/>
+      <c r="I17" s="5">
         <v>2.2886277341208801E-3</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="5">
         <v>3.8350400000000007E-2</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>2.2803199999999996E-2</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="A18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="10">
         <v>15</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="11">
         <v>44775.078923611109</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>10.092000000000001</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>31.7</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="12">
         <v>22.819885899999999</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="12">
         <v>2.718</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="12">
         <v>3.3278897669999998</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="12">
+      <c r="A19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="10">
         <v>16</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="11">
         <v>44775.079050925924</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="12">
         <v>10.382999999999999</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>93.36</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="12">
         <v>66.633761109999995</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="12">
         <v>2.6819999999999999</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="12">
         <v>6.6628506349999999</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="12">
+      <c r="A20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="10">
         <v>17</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="11">
         <v>44775.07916666667</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <v>21.992000000000001</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>229.76</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <v>162.5418607</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="12">
         <v>2.6440000000000001</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="12">
         <v>12.04121088</v>
       </c>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="12">
+      <c r="A21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="10">
         <v>18</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="11">
         <v>44775.079282407409</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="12">
         <v>18.317</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>127.13</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <v>89.561960589999998</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="12">
         <v>2.7519999999999998</v>
       </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="12">
+      <c r="A22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="10">
         <v>19</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="11">
         <v>44775.079398148147</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="12">
         <v>15.983000000000001</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>187.73</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="12">
         <v>87.538194730000001</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="12">
         <v>2.8079999999999998</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="12">
         <v>8.058197302</v>
       </c>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="12">
+      <c r="A23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="10">
         <v>20</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="11">
         <v>44775.079513888886</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="12">
         <v>14.525</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="12">
         <v>112.47</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="12">
         <v>67.359667360000003</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="12">
         <v>3.0089999999999999</v>
       </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="12">
+      <c r="A24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="10">
         <v>21</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="11">
         <v>44775.079629629632</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <v>13.532999999999999</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>84.69</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="12">
         <v>61.637080869999998</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="12">
         <v>2.7839999999999998</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="12">
+      <c r="A25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="10">
         <v>22</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="11">
         <v>44775.079745370371</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="12">
         <v>13.708</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="12">
         <v>97.42</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="12">
         <v>37.633968750000001</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="12">
         <v>2.7559999999999998</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="12">
         <v>5.0565465879999998</v>
       </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="12">
+      <c r="A26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="10">
         <v>23</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="11">
         <v>44775.079861111109</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <v>12.775</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="12">
         <v>78.81</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="12">
         <v>49.685326269999997</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="12">
         <v>2.8039999999999998</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="12">
         <v>3.736428037</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="12">
+      <c r="A27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="10">
         <v>24</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="11">
         <v>44775.079976851855</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <v>12.132999999999999</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="12">
         <v>72.819999999999993</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="12">
         <v>30.500370950000001</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="12">
         <v>2.8039999999999998</v>
       </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="12">
+      <c r="A28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="10">
         <v>25</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="11">
         <v>44775.080092592594</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="12">
         <v>12.132999999999999</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="12">
         <v>55.81</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="12">
         <v>27.990450320000001</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="12">
         <v>2.8639999999999999</v>
       </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="12">
+      <c r="A29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="10">
         <v>26</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="11">
         <v>44775.080208333333</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="12">
         <v>11.958</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="12">
         <v>45.61</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="12">
         <v>16.57275439</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="12">
         <v>2.76</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="12">
         <v>2.771444281</v>
       </c>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="12">
+      <c r="A30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10">
         <v>27</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="11">
         <v>44775.080324074072</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="12">
         <v>11.317</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="12">
         <v>47.12</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>18.368539699999999</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="12">
         <v>2.7690000000000001</v>
       </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="12">
+      <c r="A31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10">
         <v>28</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="11">
         <v>44775.080439814818</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <v>11.667</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="12">
         <v>34.58</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <v>6.458383789</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="12">
         <v>2.7410000000000001</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="12">
+      <c r="A32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="10">
         <v>29</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="11">
         <v>44775.080555555556</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <v>11.667</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="12">
         <v>34.630000000000003</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <v>11.36179192</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="12">
         <v>2.7519999999999998</v>
       </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="12">
+      <c r="A33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="10">
         <v>30</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="11">
         <v>44775.080671296295</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="12">
         <v>11.492000000000001</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="12">
         <v>36.229999999999997</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <v>11.501807429999999</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="12">
         <v>2.7389999999999999</v>
       </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="15">
+      <c r="A34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="13">
         <v>31</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="14">
         <v>44775.104745370372</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="15">
         <v>8.3420000000000005</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="15">
         <v>64.61</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="15">
         <v>52.16959258</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="15">
         <v>2.8980000000000001</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="15">
         <v>4.5952285179999999</v>
       </c>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="15">
+      <c r="A35" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="13">
         <v>32</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="14">
         <v>44775.104861111111</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="15">
         <v>21.641999999999999</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="15">
         <v>275.95999999999998</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="15">
         <v>174.6761387</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="15">
         <v>2.7160000000000002</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="15">
         <v>10.93014432</v>
       </c>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="15">
+      <c r="A36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="13">
         <v>33</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="14">
         <v>44775.10497685185</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="15">
         <v>16.917000000000002</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="15">
         <v>159.29</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="15">
         <v>78.177538670000004</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="15">
         <v>2.7010000000000001</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="15">
+      <c r="A37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="13">
         <v>34</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="14">
         <v>44775.105092592596</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="15">
         <v>14.175000000000001</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="15">
         <v>121.26</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="15">
         <v>74.758733179999993</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="15">
         <v>2.7810000000000001</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="15">
         <v>8.9789966309999993</v>
       </c>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="15">
+      <c r="A38" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="13">
         <v>35</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="14">
         <v>44775.105208333334</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="15">
         <v>12.95</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="15">
         <v>90.81</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="15">
         <v>52.974735129999999</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="15">
         <v>2.831</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="15">
+      <c r="A39" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="13">
         <v>36</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="14">
         <v>44775.105324074073</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="15">
         <v>12.6</v>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="15">
         <v>71.319999999999993</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="15">
         <v>40.183696900000001</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="15">
         <v>2.7629999999999999</v>
       </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="15">
+      <c r="A40" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="13">
         <v>37</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="14">
         <v>44775.105439814812</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="15">
         <v>11.667</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="15">
         <v>77.03</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="15">
         <v>43.398430980000001</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="15">
         <v>2.8140000000000001</v>
       </c>
-      <c r="H40" s="17">
+      <c r="H40" s="15">
         <v>4.599424687</v>
       </c>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="15">
+      <c r="A41" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="13">
         <v>38</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="14">
         <v>44775.105555555558</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="15">
         <v>13.242000000000001</v>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="15">
         <v>143.56</v>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="15">
         <v>77.334430280000007</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="15">
         <v>2.7469999999999999</v>
       </c>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="15">
+      <c r="A42" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="13">
         <v>39</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="14">
         <v>44775.105671296296</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="15">
         <v>12.775</v>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="15">
         <v>97.7</v>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="15">
         <v>58.59536189</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="15">
         <v>2.7410000000000001</v>
       </c>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="A43" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="13">
         <v>40</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="14">
         <v>44775.105787037035</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="15">
         <v>12.132999999999999</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="15">
         <v>55.95</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="15">
         <v>23.829087919999999</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="15">
         <v>2.7749999999999999</v>
       </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="15">
+      <c r="A44" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="13">
         <v>41</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="14">
         <v>44775.105902777781</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="15">
         <v>11.958</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="15">
         <v>41.32</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="15">
         <v>26.223059899999999</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="15">
         <v>2.7330000000000001</v>
       </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="15">
+      <c r="A45" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="13">
         <v>42</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="14">
         <v>44775.10601851852</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="15">
         <v>11.317</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="15">
         <v>38.15</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="15">
         <v>17.731993580000001</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="15">
         <v>2.7559999999999998</v>
       </c>
-      <c r="H45" s="17">
+      <c r="H45" s="15">
         <v>3.2584248140000001</v>
       </c>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="15">
+      <c r="A46" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="13">
         <v>43</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="14">
         <v>44775.106134259258</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="15">
         <v>11.782999999999999</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="15">
         <v>33.28</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="15">
         <v>18.922254219999999</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="15">
         <v>2.7850000000000001</v>
       </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="18">
+      <c r="A47" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="16">
         <v>44</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="17">
         <v>44776.439768518518</v>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="18">
         <v>5.3079999999999998</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="18">
         <v>90.23</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="18">
         <v>70.553888569999998</v>
       </c>
-      <c r="G47" s="20">
+      <c r="G47" s="18">
         <v>2.1829999999999998</v>
       </c>
-      <c r="H47" s="20">
+      <c r="H47" s="18">
         <v>8.3572964289999998</v>
       </c>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="18">
+      <c r="A48" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="16">
         <v>45</v>
       </c>
-      <c r="C48" s="19">
+      <c r="C48" s="17">
         <v>44776.441504629627</v>
       </c>
-      <c r="D48" s="20">
+      <c r="D48" s="18">
         <v>13.532999999999999</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="18">
         <v>526.33000000000004</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="18">
         <v>287.8289474</v>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="18">
         <v>2.1179999999999999</v>
       </c>
-      <c r="H48" s="20">
+      <c r="H48" s="18">
         <v>24.660150940000001</v>
       </c>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="18">
+      <c r="A49" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="16">
         <v>46</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C49" s="17">
         <v>44776.441562499997</v>
       </c>
-      <c r="D49" s="20">
+      <c r="D49" s="18">
         <v>14.816000000000001</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="18">
         <v>360.745</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="18">
         <v>200.0498049</v>
       </c>
-      <c r="G49" s="20">
+      <c r="G49" s="18">
         <v>2.073</v>
       </c>
-      <c r="H49" s="20">
+      <c r="H49" s="18">
         <v>16.60466516</v>
       </c>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="18">
+      <c r="A50" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="16">
         <v>47</v>
       </c>
-      <c r="C50" s="19">
+      <c r="C50" s="17">
         <v>44776.441620370373</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="18">
         <v>21.291</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="18">
         <v>168.16</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="18">
         <v>112.46027220000001</v>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="18">
         <v>2.0289999999999999</v>
       </c>
-      <c r="H50" s="20">
+      <c r="H50" s="18">
         <v>10.359493649999999</v>
       </c>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="18">
+      <c r="A51" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="16">
         <v>48</v>
       </c>
-      <c r="C51" s="19">
+      <c r="C51" s="17">
         <v>44776.441678240742</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="18">
         <v>18.140999999999998</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="18">
         <v>165.58</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="18">
         <v>111.4662733</v>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="18">
         <v>2.0779999999999998</v>
       </c>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="18">
+      <c r="A52" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="16">
         <v>49</v>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="17">
         <v>44776.441747685189</v>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="18">
         <v>15.925000000000001</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="18">
         <v>161.72</v>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="18">
         <v>79.809116340000003</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="18">
         <v>2.1640000000000001</v>
       </c>
-      <c r="H52" s="20">
+      <c r="H52" s="18">
         <v>9.2838971560000001</v>
       </c>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="18">
+      <c r="A53" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="16">
         <v>50</v>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="17">
         <v>44776.441840277781</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="18">
         <v>14</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="18">
         <v>132.56</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="18">
         <v>80.492813139999996</v>
       </c>
-      <c r="G53" s="20">
+      <c r="G53" s="18">
         <v>2.1720000000000002</v>
       </c>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="18">
+      <c r="A54" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="16">
         <v>51</v>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="17">
         <v>44776.44195601852</v>
       </c>
-      <c r="D54" s="20">
+      <c r="D54" s="18">
         <v>11.782999999999999</v>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="18">
         <v>131.22999999999999</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="18">
         <v>69.473161860000005</v>
       </c>
-      <c r="G54" s="20">
+      <c r="G54" s="18">
         <v>2.3029999999999999</v>
       </c>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="18">
+      <c r="A55" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="16">
         <v>52</v>
       </c>
-      <c r="C55" s="19">
+      <c r="C55" s="17">
         <v>44776.442083333335</v>
       </c>
-      <c r="D55" s="20">
+      <c r="D55" s="18">
         <v>10.558</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="18">
         <v>94.15</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="18">
         <v>54.027504909999998</v>
       </c>
-      <c r="G55" s="20">
+      <c r="G55" s="18">
         <v>2.2890000000000001</v>
       </c>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="18">
+      <c r="A56" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="16">
         <v>53</v>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="17">
         <v>44776.442210648151</v>
       </c>
-      <c r="D56" s="20">
+      <c r="D56" s="18">
         <v>10.382999999999999</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="18">
         <v>77.58</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="18">
         <v>44.106836559999998</v>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="18">
         <v>2.1890000000000001</v>
       </c>
-      <c r="H56" s="20">
+      <c r="H56" s="18">
         <v>5.254678427</v>
       </c>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" s="18">
+      <c r="A57" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="16">
         <v>54</v>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="17">
         <v>44776.442326388889</v>
       </c>
-      <c r="D57" s="20">
+      <c r="D57" s="18">
         <v>9.9160000000000004</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="18">
         <v>61.94</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="18">
         <v>33.532346449999999</v>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="18">
         <v>2.2829999999999999</v>
       </c>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="18">
+      <c r="A58" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="16">
         <v>55</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="17">
         <v>44776.442442129628</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="18">
         <v>9.7409999999999997</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="18">
         <v>48.68</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="18">
         <v>23.144321380000001</v>
       </c>
-      <c r="G58" s="20">
+      <c r="G58" s="18">
         <v>2.202</v>
       </c>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B59" s="21">
+      <c r="A59" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="19">
         <v>56</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="20">
         <v>44776.468287037038</v>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="21">
         <v>3.5579999999999998</v>
       </c>
-      <c r="E59" s="23">
+      <c r="E59" s="21">
         <v>90.43</v>
       </c>
-      <c r="F59" s="23">
+      <c r="F59" s="21">
         <v>62.139769450000003</v>
       </c>
-      <c r="G59" s="23">
+      <c r="G59" s="21">
         <v>2.6309999999999998</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="21">
         <v>5.3161272320000004</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="4">
         <v>8.0744786331715737E-3</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="4">
         <v>2.9254399999999986E-2</v>
       </c>
-      <c r="K59" s="5">
+      <c r="K59" s="4">
         <v>2.2803199999999996E-2</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B60" s="21">
+      <c r="A60" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="19">
         <v>57</v>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="20">
         <v>44776.471238425926</v>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="21">
         <v>7.5250000000000004</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="21">
         <v>426.28</v>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="21">
         <v>243.34662650000001</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="21">
         <v>2.581</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="21">
         <v>20.72610796</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="4">
         <v>2.3321471582393793E-2</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="4">
         <v>5.47232E-2</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K60" s="4">
         <v>1.9266599999999995E-2</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B61" s="21">
+      <c r="A61" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="19">
         <v>58</v>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="20">
         <v>44776.471296296295</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="21">
         <v>12.132999999999999</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="21">
         <v>258.72000000000003</v>
       </c>
-      <c r="F61" s="23">
+      <c r="F61" s="21">
         <v>134.52914799999999</v>
       </c>
-      <c r="G61" s="23">
+      <c r="G61" s="21">
         <v>2.5630000000000002</v>
       </c>
-      <c r="H61" s="23"/>
-      <c r="I61" s="5">
+      <c r="H61" s="21"/>
+      <c r="I61" s="4">
         <v>1.9203510472240316E-2</v>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="4">
         <v>3.28928E-2</v>
       </c>
-      <c r="K61" s="5">
+      <c r="K61" s="4">
         <v>2.2803199999999996E-2</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B62" s="21">
+      <c r="A62" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="19">
         <v>59</v>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="20">
         <v>44776.471354166664</v>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="21">
         <v>21.991</v>
       </c>
-      <c r="E62" s="23">
+      <c r="E62" s="21">
         <v>227.15</v>
       </c>
-      <c r="F62" s="23">
+      <c r="F62" s="21">
         <v>135.40290619999999</v>
       </c>
-      <c r="G62" s="23">
+      <c r="G62" s="21">
         <v>2.6619999999999999</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="21">
         <v>11.66797622</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="4">
         <v>1.15146880608244E-2</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="4">
         <v>3.4711999999999993E-2</v>
       </c>
-      <c r="K62" s="5">
+      <c r="K62" s="4">
         <v>2.2803199999999996E-2</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B63" s="21">
+      <c r="A63" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="19">
         <v>60</v>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="20">
         <v>44776.471412037034</v>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="21">
         <v>23.274999999999999</v>
       </c>
-      <c r="E63" s="23">
+      <c r="E63" s="21">
         <v>176.59</v>
       </c>
-      <c r="F63" s="23">
+      <c r="F63" s="21">
         <v>99.901736</v>
       </c>
-      <c r="G63" s="23">
+      <c r="G63" s="21">
         <v>2.6960000000000002</v>
       </c>
-      <c r="H63" s="23"/>
-      <c r="I63" s="5">
+      <c r="H63" s="21"/>
+      <c r="I63" s="4">
         <v>9.856082656835876E-3</v>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="4">
         <v>4.5627200000000007E-2</v>
       </c>
-      <c r="K63" s="5">
+      <c r="K63" s="4">
         <v>2.1034899999999995E-2</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B64" s="21">
+      <c r="A64" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="19">
         <v>61</v>
       </c>
-      <c r="C64" s="22">
+      <c r="C64" s="20">
         <v>44776.47152777778</v>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="21">
         <v>16.100000000000001</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="21">
         <v>181.06</v>
       </c>
-      <c r="F64" s="23">
+      <c r="F64" s="21">
         <v>98.606470540000004</v>
       </c>
-      <c r="G64" s="23">
+      <c r="G64" s="21">
         <v>2.6989999999999998</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="21">
         <v>6.6757924820000003</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="4">
         <v>1.16917712529308E-2</v>
       </c>
-      <c r="J64" s="5">
+      <c r="J64" s="4">
         <v>7.109600000000002E-2</v>
       </c>
-      <c r="K64" s="5">
+      <c r="K64" s="4">
         <v>2.1034899999999995E-2</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B65" s="21">
+      <c r="A65" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="19">
         <v>62</v>
       </c>
-      <c r="C65" s="22">
+      <c r="C65" s="20">
         <v>44776.471643518518</v>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="21">
         <v>13.708</v>
       </c>
-      <c r="E65" s="23">
+      <c r="E65" s="21">
         <v>157</v>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="21">
         <v>93.938898870000003</v>
       </c>
-      <c r="G65" s="23">
+      <c r="G65" s="21">
         <v>2.742</v>
       </c>
-      <c r="H65" s="23"/>
-      <c r="I65" s="5">
+      <c r="H65" s="21"/>
+      <c r="I65" s="4">
         <v>1.2283480760895546E-2</v>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="4">
         <v>8.2011200000000006E-2</v>
       </c>
-      <c r="K65" s="5">
+      <c r="K65" s="4">
         <v>1.7498300000000022E-2</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="21">
+      <c r="A66" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="19">
         <v>63</v>
       </c>
-      <c r="C66" s="22">
+      <c r="C66" s="20">
         <v>44776.471759259257</v>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="21">
         <v>12.483000000000001</v>
       </c>
-      <c r="E66" s="23">
+      <c r="E66" s="21">
         <v>134.22999999999999</v>
       </c>
-      <c r="F66" s="23">
+      <c r="F66" s="21">
         <v>56.216392370000001</v>
       </c>
-      <c r="G66" s="23">
+      <c r="G66" s="21">
         <v>2.7610000000000001</v>
       </c>
-      <c r="H66" s="23"/>
-      <c r="I66" s="5">
+      <c r="H66" s="21"/>
+      <c r="I66" s="4">
         <v>8.7555621153478178E-3</v>
       </c>
-      <c r="J66" s="5">
+      <c r="J66" s="4">
         <v>4.1988800000000021E-2</v>
       </c>
-      <c r="K66" s="5">
+      <c r="K66" s="4">
         <v>2.4571499999999996E-2</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B67" s="21">
+      <c r="A67" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="19">
         <v>64</v>
       </c>
-      <c r="C67" s="22">
+      <c r="C67" s="20">
         <v>44776.471875000003</v>
       </c>
-      <c r="D67" s="23">
+      <c r="D67" s="21">
         <v>11.375</v>
       </c>
-      <c r="E67" s="23">
+      <c r="E67" s="21">
         <v>88.31</v>
       </c>
-      <c r="F67" s="23">
+      <c r="F67" s="21">
         <v>56.813503500000003</v>
       </c>
-      <c r="G67" s="23">
+      <c r="G67" s="21">
         <v>2.8210000000000002</v>
       </c>
-      <c r="H67" s="23"/>
-      <c r="I67" s="5">
+      <c r="H67" s="21"/>
+      <c r="I67" s="4">
         <v>5.741883910742567E-3</v>
       </c>
-      <c r="J67" s="5">
+      <c r="J67" s="4">
         <v>2.9254399999999986E-2</v>
       </c>
-      <c r="K67" s="5">
+      <c r="K67" s="4">
         <v>2.4571499999999996E-2</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68" s="21">
+      <c r="A68" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="19">
         <v>65</v>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="20">
         <v>44776.471990740742</v>
       </c>
-      <c r="D68" s="23">
+      <c r="D68" s="21">
         <v>10.558</v>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="21">
         <v>88.72</v>
       </c>
-      <c r="F68" s="23">
+      <c r="F68" s="21">
         <v>48.527718370000002</v>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="21">
         <v>2.7829999999999999</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="21">
         <v>5.6309098449999997</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I68" s="4">
         <v>4.5804950914437453E-3</v>
       </c>
-      <c r="J68" s="5">
+      <c r="J68" s="4">
         <v>2.7435199999999993E-2</v>
       </c>
-      <c r="K68" s="5">
+      <c r="K68" s="4">
         <v>2.6339799999999997E-2</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69" s="21">
+      <c r="A69" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="19">
         <v>66</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="20">
         <v>44776.47210648148</v>
       </c>
-      <c r="D69" s="23">
+      <c r="D69" s="21">
         <v>10.85</v>
       </c>
-      <c r="E69" s="23">
+      <c r="E69" s="21">
         <v>71.86</v>
       </c>
-      <c r="F69" s="23">
+      <c r="F69" s="21">
         <v>41.608876559999999</v>
       </c>
-      <c r="G69" s="23">
+      <c r="G69" s="21">
         <v>2.7559999999999998</v>
       </c>
-      <c r="H69" s="23"/>
-      <c r="I69" s="5">
+      <c r="H69" s="21"/>
+      <c r="I69" s="4">
         <v>4.0576794789688791E-3</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="4">
         <v>4.3808000000000014E-2</v>
       </c>
-      <c r="K69" s="5">
+      <c r="K69" s="4">
         <v>2.1034899999999995E-2</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B70" s="21">
+      <c r="A70" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="19">
         <v>67</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="20">
         <v>44776.472222222219</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D70" s="21">
         <v>10.85</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E70" s="21">
         <v>59.21</v>
       </c>
-      <c r="F70" s="23">
+      <c r="F70" s="21">
         <v>27.029240720000001</v>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="21">
         <v>2.883</v>
       </c>
-      <c r="H70" s="23"/>
-      <c r="I70" s="5">
+      <c r="H70" s="21"/>
+      <c r="I70" s="4">
         <v>3.3758505307597045E-3</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="4">
         <v>2.7435199999999993E-2</v>
       </c>
-      <c r="K70" s="5">
+      <c r="K70" s="4">
         <v>2.2803199999999996E-2</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B71" s="21">
+      <c r="A71" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="19">
         <v>68</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="20">
         <v>44776.472337962965</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D71" s="21">
         <v>10.382999999999999</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E71" s="21">
         <v>51.52</v>
       </c>
-      <c r="F71" s="23">
+      <c r="F71" s="21">
         <v>22.11845662</v>
       </c>
-      <c r="G71" s="23">
+      <c r="G71" s="21">
         <v>2.84</v>
       </c>
-      <c r="H71" s="23"/>
-      <c r="I71" s="5">
+      <c r="H71" s="21"/>
+      <c r="I71" s="4">
         <v>3.4794954752049401E-3</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="4">
         <v>3.1073600000000007E-2</v>
       </c>
-      <c r="K71" s="5">
+      <c r="K71" s="4">
         <v>2.4571499999999996E-2</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" s="24">
+      <c r="A72" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="22">
         <v>69</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="23">
         <v>44777.082615740743</v>
       </c>
-      <c r="D72" s="26">
+      <c r="D72" s="24">
         <v>8.4580000000000002</v>
       </c>
-      <c r="E72" s="26">
+      <c r="E72" s="24">
         <v>0</v>
       </c>
-      <c r="F72" s="26">
+      <c r="F72" s="24">
         <v>25.420254199999999</v>
       </c>
-      <c r="G72" s="26">
+      <c r="G72" s="24">
         <v>2.9359999999999999</v>
       </c>
-      <c r="H72" s="26">
+      <c r="H72" s="24">
         <v>3.6469399779999998</v>
       </c>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
+      <c r="I72" s="24"/>
+      <c r="J72" s="24"/>
+      <c r="K72" s="24"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73" s="24">
+      <c r="A73" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="22">
         <v>70</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="23">
         <v>44777.083969907406</v>
       </c>
-      <c r="D73" s="26">
+      <c r="D73" s="24">
         <v>8.6329999999999991</v>
       </c>
-      <c r="E73" s="26">
+      <c r="E73" s="24">
         <v>0</v>
       </c>
-      <c r="F73" s="26">
+      <c r="F73" s="24">
         <v>9.0053213260000007</v>
       </c>
-      <c r="G73" s="26">
+      <c r="G73" s="24">
         <v>3.0289999999999999</v>
       </c>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="24"/>
+      <c r="K73" s="24"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" s="24">
+      <c r="A74" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="22">
         <v>71</v>
       </c>
-      <c r="C74" s="25">
+      <c r="C74" s="23">
         <v>44777.084004629629</v>
       </c>
-      <c r="D74" s="26">
+      <c r="D74" s="24">
         <v>8.8079999999999998</v>
       </c>
-      <c r="E74" s="26">
+      <c r="E74" s="24">
         <v>0</v>
       </c>
-      <c r="F74" s="26">
+      <c r="F74" s="24">
         <v>7.4868979290000004</v>
       </c>
-      <c r="G74" s="26">
+      <c r="G74" s="24">
         <v>2.923</v>
       </c>
-      <c r="H74" s="26">
+      <c r="H74" s="24">
         <v>2.38341665</v>
       </c>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B75" s="24">
+      <c r="A75" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="22">
         <v>72</v>
       </c>
-      <c r="C75" s="25">
+      <c r="C75" s="23">
         <v>44777.084039351852</v>
       </c>
-      <c r="D75" s="26">
+      <c r="D75" s="24">
         <v>9.0419999999999998</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="24">
         <v>0</v>
       </c>
-      <c r="F75" s="26">
+      <c r="F75" s="24">
         <v>4.9549921550000002</v>
       </c>
-      <c r="G75" s="26">
+      <c r="G75" s="24">
         <v>2.976</v>
       </c>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="24"/>
+      <c r="K75" s="24"/>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" s="24">
+      <c r="A76" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="22">
         <v>73</v>
       </c>
-      <c r="C76" s="25">
+      <c r="C76" s="23">
         <v>44777.084074074075</v>
       </c>
-      <c r="D76" s="26">
+      <c r="D76" s="24">
         <v>9.9169999999999998</v>
       </c>
-      <c r="E76" s="26">
+      <c r="E76" s="24">
         <v>0</v>
       </c>
-      <c r="F76" s="26">
+      <c r="F76" s="24">
         <v>7.3004542499999996</v>
       </c>
-      <c r="G76" s="26">
+      <c r="G76" s="24">
         <v>3.641</v>
       </c>
-      <c r="H76" s="26">
+      <c r="H76" s="24">
         <v>2.1756635950000001</v>
       </c>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="24"/>
+      <c r="K76" s="24"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77" s="24">
+      <c r="A77" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="22">
         <v>74</v>
       </c>
-      <c r="C77" s="25">
+      <c r="C77" s="23">
         <v>44777.084108796298</v>
       </c>
-      <c r="D77" s="26">
+      <c r="D77" s="24">
         <v>10.092000000000001</v>
       </c>
-      <c r="E77" s="26">
+      <c r="E77" s="24">
         <v>70.88</v>
       </c>
-      <c r="F77" s="26">
+      <c r="F77" s="24">
         <v>31.924724860000001</v>
       </c>
-      <c r="G77" s="26">
+      <c r="G77" s="24">
         <v>3.0539999999999998</v>
       </c>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="24"/>
+      <c r="K77" s="24"/>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" s="24">
+      <c r="A78" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="22">
         <v>75</v>
       </c>
-      <c r="C78" s="25">
+      <c r="C78" s="23">
         <v>44777.084143518521</v>
       </c>
-      <c r="D78" s="26">
+      <c r="D78" s="24">
         <v>10.442</v>
       </c>
-      <c r="E78" s="26">
+      <c r="E78" s="24">
         <v>73.459999999999994</v>
       </c>
-      <c r="F78" s="26">
+      <c r="F78" s="24">
         <v>41.421588929999999</v>
       </c>
-      <c r="G78" s="26">
+      <c r="G78" s="24">
         <v>3.0379999999999998</v>
       </c>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24"/>
+      <c r="J78" s="24"/>
+      <c r="K78" s="24"/>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" s="24">
+      <c r="A79" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="22">
         <v>76</v>
       </c>
-      <c r="C79" s="25">
+      <c r="C79" s="23">
         <v>44777.084178240744</v>
       </c>
-      <c r="D79" s="26">
+      <c r="D79" s="24">
         <v>10.617000000000001</v>
       </c>
-      <c r="E79" s="26">
+      <c r="E79" s="24">
         <v>84.58</v>
       </c>
-      <c r="F79" s="26">
+      <c r="F79" s="24">
         <v>44.890630100000003</v>
       </c>
-      <c r="G79" s="26">
+      <c r="G79" s="24">
         <v>3.5790000000000002</v>
       </c>
-      <c r="H79" s="26">
+      <c r="H79" s="24">
         <v>4.7777531050000004</v>
       </c>
-      <c r="I79" s="26"/>
-      <c r="J79" s="26"/>
-      <c r="K79" s="26"/>
+      <c r="I79" s="24"/>
+      <c r="J79" s="24"/>
+      <c r="K79" s="24"/>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" s="24">
+      <c r="A80" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="22">
         <v>77</v>
       </c>
-      <c r="C80" s="25">
+      <c r="C80" s="23">
         <v>44777.08421296296</v>
       </c>
-      <c r="D80" s="26">
+      <c r="D80" s="24">
         <v>10.442</v>
       </c>
-      <c r="E80" s="26">
+      <c r="E80" s="24">
         <v>67.36</v>
       </c>
-      <c r="F80" s="26">
+      <c r="F80" s="24">
         <v>33.184005310000003</v>
       </c>
-      <c r="G80" s="26">
+      <c r="G80" s="24">
         <v>3.1509999999999998</v>
       </c>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" s="24">
+      <c r="A81" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="22">
         <v>78</v>
       </c>
-      <c r="C81" s="25">
+      <c r="C81" s="23">
         <v>44777.084247685183</v>
       </c>
-      <c r="D81" s="26">
+      <c r="D81" s="24">
         <v>10.092000000000001</v>
       </c>
-      <c r="E81" s="26">
+      <c r="E81" s="24">
         <v>65.8</v>
       </c>
-      <c r="F81" s="26">
+      <c r="F81" s="24">
         <v>25.368248770000001</v>
       </c>
-      <c r="G81" s="26">
+      <c r="G81" s="24">
         <v>3.0059999999999998</v>
       </c>
-      <c r="H81" s="26">
+      <c r="H81" s="24">
         <v>4.9322235059999997</v>
       </c>
-      <c r="I81" s="26"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="26"/>
+      <c r="I81" s="24"/>
+      <c r="J81" s="24"/>
+      <c r="K81" s="24"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" s="24">
+      <c r="A82" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="22">
         <v>79</v>
       </c>
-      <c r="C82" s="25">
+      <c r="C82" s="23">
         <v>44777.084282407406</v>
       </c>
-      <c r="D82" s="26">
+      <c r="D82" s="24">
         <v>9.9169999999999998</v>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="24">
         <v>65.319999999999993</v>
       </c>
-      <c r="F82" s="26">
+      <c r="F82" s="24">
         <v>6.5455735559999999</v>
       </c>
-      <c r="G82" s="26">
+      <c r="G82" s="24">
         <v>3.5510000000000002</v>
       </c>
-      <c r="H82" s="26"/>
-      <c r="I82" s="26"/>
-      <c r="J82" s="26"/>
-      <c r="K82" s="26"/>
+      <c r="H82" s="24"/>
+      <c r="I82" s="24"/>
+      <c r="J82" s="24"/>
+      <c r="K82" s="24"/>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B83" s="9">
+      <c r="A83" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" s="7">
         <v>85</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="8">
         <v>44778.468946759262</v>
       </c>
-      <c r="D83" s="27">
+      <c r="D83" s="25">
         <v>7.2329999999999997</v>
       </c>
-      <c r="E83" s="27">
+      <c r="E83" s="25">
         <v>94.93</v>
       </c>
-      <c r="F83" s="27">
+      <c r="F83" s="25">
         <v>46.45476773</v>
       </c>
-      <c r="G83" s="27">
+      <c r="G83" s="25">
         <v>3.0339999999999998</v>
       </c>
-      <c r="H83" s="27">
+      <c r="H83" s="25">
         <v>5.5154976969999998</v>
       </c>
-      <c r="I83" s="27"/>
-      <c r="J83" s="27"/>
-      <c r="K83" s="27"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B84" s="9">
+      <c r="A84" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" s="7">
         <v>86</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="8">
         <v>44778.468981481485</v>
       </c>
-      <c r="D84" s="27">
+      <c r="D84" s="25">
         <v>7.2329999999999997</v>
       </c>
-      <c r="E84" s="27">
+      <c r="E84" s="25">
         <v>75.03</v>
       </c>
-      <c r="F84" s="27">
+      <c r="F84" s="25">
         <v>42.016806719999998</v>
       </c>
-      <c r="G84" s="27">
+      <c r="G84" s="25">
         <v>3.0539999999999998</v>
       </c>
-      <c r="H84" s="27"/>
-      <c r="I84" s="27"/>
-      <c r="J84" s="27"/>
-      <c r="K84" s="27"/>
+      <c r="H84" s="25"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B85" s="9">
+      <c r="A85" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" s="7">
         <v>87</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="8">
         <v>44778.4690162037</v>
       </c>
-      <c r="D85" s="27">
+      <c r="D85" s="25">
         <v>7.9329999999999998</v>
       </c>
-      <c r="E85" s="27">
+      <c r="E85" s="25">
         <v>81.28</v>
       </c>
-      <c r="F85" s="27">
+      <c r="F85" s="25">
         <v>43.243243239999998</v>
       </c>
-      <c r="G85" s="27">
+      <c r="G85" s="25">
         <v>2.4729999999999999</v>
       </c>
-      <c r="H85" s="27">
+      <c r="H85" s="25">
         <v>3.927531906</v>
       </c>
-      <c r="I85" s="27"/>
-      <c r="J85" s="27"/>
-      <c r="K85" s="27"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B86" s="9">
+      <c r="A86" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86" s="7">
         <v>88</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="8">
         <v>44778.469050925924</v>
       </c>
-      <c r="D86" s="27">
+      <c r="D86" s="25">
         <v>9.3919999999999995</v>
       </c>
-      <c r="E86" s="27">
+      <c r="E86" s="25">
         <v>293.19</v>
       </c>
-      <c r="F86" s="27">
+      <c r="F86" s="25">
         <v>144.48979589999999</v>
       </c>
-      <c r="G86" s="27">
+      <c r="G86" s="25">
         <v>2.6160000000000001</v>
       </c>
-      <c r="H86" s="27"/>
-      <c r="I86" s="27"/>
-      <c r="J86" s="27"/>
-      <c r="K86" s="27"/>
+      <c r="H86" s="25"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B87" s="9">
+      <c r="A87" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B87" s="7">
         <v>89</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="8">
         <v>44778.469085648147</v>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="25">
         <v>9.3919999999999995</v>
       </c>
-      <c r="E87" s="27">
+      <c r="E87" s="25">
         <v>311.7</v>
       </c>
-      <c r="F87" s="27">
+      <c r="F87" s="25">
         <v>240.01979539999999</v>
       </c>
-      <c r="G87" s="27">
+      <c r="G87" s="25">
         <v>3.1349999999999998</v>
       </c>
-      <c r="H87" s="27">
+      <c r="H87" s="25">
         <v>15.122709800000001</v>
       </c>
-      <c r="I87" s="27"/>
-      <c r="J87" s="27"/>
-      <c r="K87" s="27"/>
+      <c r="I87" s="25"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="25"/>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B88" s="9">
+      <c r="A88" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" s="7">
         <v>90</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="8">
         <v>44778.46912037037</v>
       </c>
-      <c r="D88" s="27">
+      <c r="D88" s="25">
         <v>9.3919999999999995</v>
       </c>
-      <c r="E88" s="27">
+      <c r="E88" s="25">
         <v>243.92</v>
       </c>
-      <c r="F88" s="27">
+      <c r="F88" s="25">
         <v>191.19209090000001</v>
       </c>
-      <c r="G88" s="27">
+      <c r="G88" s="25">
         <v>2.9359999999999999</v>
       </c>
-      <c r="H88" s="27"/>
-      <c r="I88" s="27"/>
-      <c r="J88" s="27"/>
-      <c r="K88" s="27"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="25"/>
+      <c r="J88" s="25"/>
+      <c r="K88" s="25"/>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B89" s="9">
+      <c r="A89" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" s="7">
         <v>91</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="8">
         <v>44778.469155092593</v>
       </c>
-      <c r="D89" s="27">
+      <c r="D89" s="25">
         <v>9.3919999999999995</v>
       </c>
-      <c r="E89" s="27">
+      <c r="E89" s="25">
         <v>292.16000000000003</v>
       </c>
-      <c r="F89" s="27">
+      <c r="F89" s="25">
         <v>164.10842589999999</v>
       </c>
-      <c r="G89" s="27">
+      <c r="G89" s="25">
         <v>2.9329999999999998</v>
       </c>
-      <c r="H89" s="27">
+      <c r="H89" s="25">
         <v>17.196570690000001</v>
       </c>
-      <c r="I89" s="27"/>
-      <c r="J89" s="27"/>
-      <c r="K89" s="27"/>
+      <c r="I89" s="25"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="25"/>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B90" s="9">
+      <c r="A90" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" s="7">
         <v>92</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="8">
         <v>44778.469189814816</v>
       </c>
-      <c r="D90" s="27">
+      <c r="D90" s="25">
         <v>9.0419999999999998</v>
       </c>
-      <c r="E90" s="27">
+      <c r="E90" s="25">
         <v>260.11</v>
       </c>
-      <c r="F90" s="27">
+      <c r="F90" s="25">
         <v>119.19751530000001</v>
       </c>
-      <c r="G90" s="27">
+      <c r="G90" s="25">
         <v>2.6339999999999999</v>
       </c>
-      <c r="H90" s="27">
+      <c r="H90" s="25">
         <v>9.5060401779999992</v>
       </c>
-      <c r="I90" s="27"/>
-      <c r="J90" s="27"/>
-      <c r="K90" s="27"/>
+      <c r="I90" s="25"/>
+      <c r="J90" s="25"/>
+      <c r="K90" s="25"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B91" s="9">
+      <c r="A91" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" s="7">
         <v>93</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="8">
         <v>44778.469259259262</v>
       </c>
-      <c r="D91" s="27">
+      <c r="D91" s="25">
         <v>8.4580000000000002</v>
       </c>
-      <c r="E91" s="27">
+      <c r="E91" s="25">
         <v>194.51</v>
       </c>
-      <c r="F91" s="27">
+      <c r="F91" s="25">
         <v>96.298777419999993</v>
       </c>
-      <c r="G91" s="27">
+      <c r="G91" s="25">
         <v>2.97</v>
       </c>
-      <c r="H91" s="27">
+      <c r="H91" s="25">
         <v>6.3675166709999997</v>
       </c>
-      <c r="I91" s="27"/>
-      <c r="J91" s="27"/>
-      <c r="K91" s="27"/>
+      <c r="I91" s="25"/>
+      <c r="J91" s="25"/>
+      <c r="K91" s="25"/>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B92" s="9">
+      <c r="A92" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" s="7">
         <v>94</v>
       </c>
-      <c r="C92" s="10">
+      <c r="C92" s="8">
         <v>44778.469293981485</v>
       </c>
-      <c r="D92" s="27">
+      <c r="D92" s="25">
         <v>8.2829999999999995</v>
       </c>
-      <c r="E92" s="27">
+      <c r="E92" s="25">
         <v>189.68</v>
       </c>
-      <c r="F92" s="27">
+      <c r="F92" s="25">
         <v>96.842105259999997</v>
       </c>
-      <c r="G92" s="27">
+      <c r="G92" s="25">
         <v>2.4969999999999999</v>
       </c>
-      <c r="H92" s="27"/>
-      <c r="I92" s="27"/>
-      <c r="J92" s="27"/>
-      <c r="K92" s="27"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="25"/>
+      <c r="J92" s="25"/>
+      <c r="K92" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
+++ b/experiments/HI_calculations/pulse_experiment_HI_summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\experiments\HI_calculations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\experiments\HI_calculations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7460BE-8AC0-4B00-BD8D-581DBB265705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFD4490-D255-427A-9DA0-010D5F99CBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{79B9BBCE-B8B3-479F-8F8D-5E0698834AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,9 +143,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -242,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -253,10 +253,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -268,7 +268,7 @@
     <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -277,7 +277,7 @@
     <xf numFmtId="22" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -286,7 +286,7 @@
     <xf numFmtId="22" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -295,7 +295,7 @@
     <xf numFmtId="22" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -304,7 +304,7 @@
     <xf numFmtId="22" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -328,41 +328,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1054,7 +1044,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.453436795025429</c:v>
@@ -1641,7 +1631,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.262211557214444</c:v>
@@ -2228,7 +2218,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$23:$B$27</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>8.2872285708523799E-2</c:v>
@@ -2772,7 +2762,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.453436795025429</c:v>
@@ -2796,7 +2786,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.262211557214444</c:v>
@@ -2855,7 +2845,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2917,7 +2907,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3174,7 +3164,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.453436795025429</c:v>
@@ -3317,7 +3307,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -18457,7 +18447,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.453436795025429</c:v>
@@ -19033,7 +19023,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.262211557214444</c:v>
@@ -19609,7 +19599,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$23:$B$27</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>8.2872285708523799E-2</c:v>
@@ -20198,7 +20188,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$5:$B$9</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.453436795025429</c:v>
@@ -20785,7 +20775,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$18</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.262211557214444</c:v>
@@ -21372,7 +21362,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$23:$B$27</c:f>
               <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>8.2872285708523799E-2</c:v>
@@ -43866,7 +43856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
@@ -43879,9 +43869,10 @@
     <col min="8" max="8" width="21.85546875" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -43892,7 +43883,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>9</v>
       </c>
@@ -43918,12 +43909,13 @@
       <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="O4" s="33"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="35">
         <v>0.453436795025429</v>
       </c>
       <c r="C5" s="6">
@@ -43950,12 +43942,13 @@
       <c r="J5" s="6">
         <v>85.714285714285708</v>
       </c>
+      <c r="O5" s="33"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="35">
         <v>0.14144997157405101</v>
       </c>
       <c r="C6" s="6">
@@ -43982,12 +43975,13 @@
       <c r="J6" s="6">
         <v>61.53846153846154</v>
       </c>
+      <c r="O6" s="33"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="35">
         <v>0.13607881876945299</v>
       </c>
       <c r="C7" s="6">
@@ -44014,12 +44008,13 @@
       <c r="J7" s="6">
         <v>30.76923076923077</v>
       </c>
+      <c r="O7" s="33"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="35">
         <v>0.61769731984154397</v>
       </c>
       <c r="C8" s="6">
@@ -44046,12 +44041,13 @@
       <c r="J8" s="6">
         <v>40</v>
       </c>
+      <c r="O8" s="33"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="37">
         <v>0.66455526442613699</v>
       </c>
       <c r="C9" s="30">
@@ -44078,13 +44074,14 @@
       <c r="J9" s="30">
         <v>33.333333333333329</v>
       </c>
+      <c r="O9" s="33"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
-        <v>0.15353684539821699</v>
+      <c r="B10" s="35">
+        <v>0.108961953015194</v>
       </c>
       <c r="C10" s="6">
         <f>MAX('constituent correlations'!F72:F82)</f>
@@ -44111,12 +44108,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="5">
-        <v>-0.28559783552715301</v>
+      <c r="B11" s="35">
+        <v>0.110130855336203</v>
       </c>
       <c r="C11" s="6">
         <f>MAX('constituent correlations'!F83:F92)</f>
@@ -44145,11 +44142,13 @@
       <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="O11" s="33"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I12" s="1"/>
+      <c r="O12" s="33"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>1</v>
       </c>
@@ -44160,12 +44159,13 @@
         <v>23</v>
       </c>
       <c r="D13" s="1"/>
+      <c r="O13" s="33"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="35">
         <v>0.262211557214444</v>
       </c>
       <c r="C14" s="6">
@@ -44174,11 +44174,11 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="35">
         <v>0.15997395020695501</v>
       </c>
       <c r="C15" s="6">
@@ -44186,12 +44186,13 @@
         <v>12.04121088</v>
       </c>
       <c r="D15" s="1"/>
+      <c r="O15" s="33"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="31">
         <v>-2.5566841037180299E-3</v>
       </c>
       <c r="C16" s="6">
@@ -44199,12 +44200,13 @@
         <v>10.93014432</v>
       </c>
       <c r="D16" s="1"/>
+      <c r="O16" s="33"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="35">
         <v>0.62020718230999505</v>
       </c>
       <c r="C17" s="6">
@@ -44212,12 +44214,13 @@
         <v>24.660150940000001</v>
       </c>
       <c r="D17" s="1"/>
+      <c r="O17" s="33"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="37">
         <v>0.78199948801270402</v>
       </c>
       <c r="C18" s="30">
@@ -44226,11 +44229,11 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="31">
         <v>-0.501279910362319</v>
       </c>
       <c r="C19" s="6">
@@ -44238,13 +44241,14 @@
         <v>4.9322235059999997</v>
       </c>
       <c r="D19" s="1"/>
+      <c r="O19" s="33"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="4">
-        <v>0.14455219387620799</v>
+      <c r="B20" s="35">
+        <v>9.1527185590156004E-2</v>
       </c>
       <c r="C20" s="6">
         <f>MAX('constituent correlations'!H83:H92)</f>
@@ -44254,8 +44258,12 @@
         <f>C19/C20</f>
         <v>0.28681436519597148</v>
       </c>
+      <c r="O20" s="33"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O21" s="33"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
         <v>0</v>
       </c>
@@ -44267,11 +44275,11 @@
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="35">
         <v>8.2872285708523799E-2</v>
       </c>
       <c r="C23" s="1">
@@ -44279,12 +44287,13 @@
         <v>2.64</v>
       </c>
       <c r="D23" s="1"/>
+      <c r="O23" s="33"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="31">
         <v>-0.120864394889326</v>
       </c>
       <c r="C24" s="1">
@@ -44292,12 +44301,13 @@
         <v>3.0089999999999999</v>
       </c>
       <c r="D24" s="1"/>
+      <c r="O24" s="33"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="35">
         <v>1.1974710137234199E-2</v>
       </c>
       <c r="C25" s="1">
@@ -44305,12 +44315,13 @@
         <v>2.8980000000000001</v>
       </c>
       <c r="D25" s="1"/>
+      <c r="O25" s="33"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="31">
         <v>-9.3327819128066702E-2</v>
       </c>
       <c r="C26" s="1">
@@ -44318,12 +44329,13 @@
         <v>2.3029999999999999</v>
       </c>
       <c r="D26" s="1"/>
+      <c r="O26" s="33"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="34">
         <v>-7.3285474508812898E-2</v>
       </c>
       <c r="C27" s="28">
@@ -44331,12 +44343,13 @@
         <v>2.883</v>
       </c>
       <c r="D27" s="1"/>
+      <c r="O27" s="33"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="31">
         <v>-8.6314057587169295E-3</v>
       </c>
       <c r="C28" s="6">
@@ -44344,13 +44357,14 @@
         <v>3.641</v>
       </c>
       <c r="D28" s="1"/>
+      <c r="O28" s="33"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4">
-        <v>4.5754279708113597E-2</v>
+      <c r="B29" s="35">
+        <v>0.11666545665484999</v>
       </c>
       <c r="C29" s="6">
         <f>MAX('constituent correlations'!G83:G92)</f>
@@ -44361,7 +44375,10 @@
         <v>1.1614035087719299</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O30" s="33"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
         <v>29</v>
       </c>
@@ -44372,78 +44389,83 @@
         <v>23</v>
       </c>
       <c r="D31" s="1"/>
+      <c r="O31" s="33"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="4">
         <v>0.39025509275430098</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="33">
         <v>2.2338385851655443E-2</v>
       </c>
       <c r="D32" s="1"/>
+      <c r="O32" s="33"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="1"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33"/>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="1"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="33"/>
       <c r="D34" s="1"/>
+      <c r="O34" s="33"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="1"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="33"/>
       <c r="D35" s="1"/>
+      <c r="O35" s="33"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="29">
         <v>0.54200255292126898</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="36">
         <v>2.3321471582393793E-2</v>
       </c>
       <c r="D36" s="1"/>
+      <c r="O36" s="33"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="34"/>
+      <c r="B37" s="32"/>
       <c r="C37" s="6"/>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="34"/>
+      <c r="B38" s="32"/>
       <c r="C38" s="6"/>
       <c r="D38" s="1" t="e">
         <f>C37/C38</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B39" s="1"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
         <v>31</v>
       </c>
@@ -44454,75 +44476,74 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="5">
         <v>-0.26955872659063201</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="33">
         <v>2.9876399999999997E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="36"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="33"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="36"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="33"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="36"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="33"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
         <v>7</v>
       </c>
       <c r="B45" s="29">
         <v>2.6807256740673498E-3</v>
       </c>
-      <c r="C45" s="37">
+      <c r="C45" s="36">
         <v>2.6339799999999997E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B46" s="34"/>
-      <c r="C46" s="38"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="6"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="38"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="6"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="36"/>
-      <c r="C48" s="39"/>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -44530,10 +44551,10 @@
       <c r="A50" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="31">
         <v>-0.33213619826679402</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="33">
         <v>8.9288000000000034E-2</v>
       </c>
     </row>
@@ -44541,31 +44562,31 @@
       <c r="A51" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="36"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B52" s="40"/>
-      <c r="C52" s="36"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="40"/>
-      <c r="C53" s="36"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="41">
+      <c r="B54" s="34">
         <v>-0.235823563048565</v>
       </c>
-      <c r="C54" s="37">
+      <c r="C54" s="36">
         <v>8.2011200000000006E-2</v>
       </c>
     </row>
@@ -44573,15 +44594,15 @@
       <c r="A55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="38"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="6"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="38"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
